--- a/01_proyecto/trim1/01_contextualizacion_proyecto/PL01 - Plantilla de Definición.xlsx
+++ b/01_proyecto/trim1/01_contextualizacion_proyecto/PL01 - Plantilla de Definición.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZUS\Desktop\hola\Innovation_Fusion\01_proyecto\trim1\01_contextualizacion_proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44D7A5E-0DBD-40B3-92BF-25A5AE879B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1EEFEB-2C38-4485-9671-A4BD5EDAADB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipo" sheetId="1" r:id="rId1"/>
@@ -623,7 +623,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -675,6 +675,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA4C2F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -819,7 +825,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -859,9 +865,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -883,6 +886,9 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -901,6 +907,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2367,15 +2375,15 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
     </row>
     <row r="5" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
@@ -2493,15 +2501,15 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="8" t="s">
@@ -2665,15 +2673,15 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
     </row>
     <row r="19" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
@@ -2745,15 +2753,15 @@
       </c>
     </row>
     <row r="22" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
     </row>
     <row r="23" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
@@ -2779,15 +2787,15 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
     </row>
     <row r="25" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
@@ -2997,15 +3005,15 @@
       </c>
     </row>
     <row r="34" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
     </row>
     <row r="35" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
@@ -3100,15 +3108,15 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
     </row>
     <row r="40" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
@@ -3157,15 +3165,15 @@
       </c>
     </row>
     <row r="42" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
     </row>
     <row r="43" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
@@ -3191,15 +3199,15 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
     </row>
     <row r="45" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
@@ -4205,57 +4213,126 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D6B611-C79A-4628-842F-788DD2B12556}">
-  <dimension ref="A1:AG38"/>
+  <dimension ref="A1:AJ38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="3" max="3" width="7.42578125" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
-    </row>
-    <row r="2" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="D1" s="31">
+        <v>45979</v>
+      </c>
+      <c r="E1" s="31">
+        <v>45980</v>
+      </c>
+      <c r="F1" s="31">
+        <v>45981</v>
+      </c>
+      <c r="G1" s="31">
+        <v>45982</v>
+      </c>
+      <c r="H1" s="31">
+        <v>45983</v>
+      </c>
+      <c r="I1" s="31">
+        <v>45984</v>
+      </c>
+      <c r="J1" s="31">
+        <v>45985</v>
+      </c>
+      <c r="K1" s="31">
+        <v>45986</v>
+      </c>
+      <c r="L1" s="31">
+        <v>45987</v>
+      </c>
+      <c r="M1" s="31">
+        <v>45988</v>
+      </c>
+      <c r="N1" s="31">
+        <v>45989</v>
+      </c>
+      <c r="O1" s="31">
+        <v>45990</v>
+      </c>
+      <c r="P1" s="31">
+        <v>45991</v>
+      </c>
+      <c r="Q1" s="31">
+        <v>45992</v>
+      </c>
+      <c r="R1" s="31">
+        <v>45993</v>
+      </c>
+      <c r="S1" s="31">
+        <v>45994</v>
+      </c>
+      <c r="T1" s="31">
+        <v>45995</v>
+      </c>
+      <c r="U1" s="31">
+        <v>45996</v>
+      </c>
+      <c r="V1" s="31">
+        <v>45997</v>
+      </c>
+      <c r="W1" s="31">
+        <v>45998</v>
+      </c>
+      <c r="X1" s="31">
+        <v>45999</v>
+      </c>
+      <c r="Y1" s="31">
+        <v>46000</v>
+      </c>
+      <c r="Z1" s="31">
+        <v>46001</v>
+      </c>
+      <c r="AA1" s="31">
+        <v>46002</v>
+      </c>
+      <c r="AB1" s="31">
+        <v>46003</v>
+      </c>
+      <c r="AC1" s="31">
+        <v>46004</v>
+      </c>
+      <c r="AD1" s="31">
+        <v>46005</v>
+      </c>
+      <c r="AE1" s="31">
+        <v>46006</v>
+      </c>
+      <c r="AF1" s="31">
+        <v>46007</v>
+      </c>
+      <c r="AG1" s="31">
+        <v>46008</v>
+      </c>
+      <c r="AH1" s="31">
+        <v>46009</v>
+      </c>
+      <c r="AI1" s="31">
+        <v>46010</v>
+      </c>
+      <c r="AJ1" s="31">
+        <v>46011</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
@@ -4292,7 +4369,7 @@
       <c r="AF2" s="11"/>
       <c r="AG2" s="11"/>
     </row>
-    <row r="3" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>44</v>
       </c>
@@ -4329,7 +4406,7 @@
       <c r="AF3" s="11"/>
       <c r="AG3" s="11"/>
     </row>
-    <row r="4" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>46</v>
       </c>
@@ -4366,7 +4443,7 @@
       <c r="AF4" s="11"/>
       <c r="AG4" s="11"/>
     </row>
-    <row r="5" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>47</v>
       </c>
@@ -4403,7 +4480,7 @@
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
     </row>
-    <row r="6" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>48</v>
       </c>
@@ -4440,7 +4517,7 @@
       <c r="AF6" s="11"/>
       <c r="AG6" s="11"/>
     </row>
-    <row r="7" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>56</v>
       </c>
@@ -4477,7 +4554,7 @@
       <c r="AF7" s="11"/>
       <c r="AG7" s="11"/>
     </row>
-    <row r="8" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" ht="57" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>63</v>
       </c>
@@ -4514,7 +4591,7 @@
       <c r="AF8" s="11"/>
       <c r="AG8" s="11"/>
     </row>
-    <row r="9" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>67</v>
       </c>
@@ -4551,7 +4628,7 @@
       <c r="AF9" s="11"/>
       <c r="AG9" s="11"/>
     </row>
-    <row r="10" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>69</v>
       </c>
@@ -4588,7 +4665,7 @@
       <c r="AF10" s="11"/>
       <c r="AG10" s="11"/>
     </row>
-    <row r="11" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>73</v>
       </c>
@@ -4625,7 +4702,7 @@
       <c r="AF11" s="11"/>
       <c r="AG11" s="11"/>
     </row>
-    <row r="12" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" ht="57" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>76</v>
       </c>
@@ -4662,7 +4739,7 @@
       <c r="AF12" s="11"/>
       <c r="AG12" s="11"/>
     </row>
-    <row r="13" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>80</v>
       </c>
@@ -4699,11 +4776,13 @@
       <c r="AF13" s="11"/>
       <c r="AG13" s="11"/>
     </row>
-    <row r="14" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="31">
+        <v>39583</v>
+      </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
@@ -4736,7 +4815,7 @@
       <c r="AF14" s="11"/>
       <c r="AG14" s="11"/>
     </row>
-    <row r="15" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>90</v>
       </c>
@@ -4773,7 +4852,7 @@
       <c r="AF15" s="11"/>
       <c r="AG15" s="11"/>
     </row>
-    <row r="16" spans="1:33" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>93</v>
       </c>
@@ -6587,148 +6666,148 @@
   <sheetData>
     <row r="2" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="18"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="20"/>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="18"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="20"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="18"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="20"/>
+      <c r="B6" s="19"/>
       <c r="C6" s="25" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="27"/>
-      <c r="F6" s="18"/>
+      <c r="F6" s="17"/>
     </row>
     <row r="7" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="20"/>
+      <c r="B7" s="19"/>
       <c r="C7" s="28"/>
       <c r="D7" s="29"/>
       <c r="E7" s="30"/>
-      <c r="F7" s="18"/>
-    </row>
-    <row r="8" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="20"/>
-      <c r="C8" s="21" t="s">
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="19"/>
+      <c r="C8" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="18"/>
+      <c r="F8" s="17"/>
     </row>
     <row r="9" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="20"/>
-      <c r="C9" s="23">
+      <c r="B9" s="19"/>
+      <c r="C9" s="22">
         <v>5</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="22">
         <v>5</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="18"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="17"/>
     </row>
     <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="20"/>
+      <c r="B10" s="19"/>
       <c r="C10" s="25" t="s">
         <v>163</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="27"/>
-      <c r="F10" s="18"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="20"/>
-      <c r="C11" s="24" t="s">
+      <c r="B11" s="19"/>
+      <c r="C11" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="F11" s="18"/>
+      <c r="F11" s="17"/>
     </row>
     <row r="12" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="20"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="20"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="20"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="17"/>
     </row>
     <row r="15" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="20"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="18"/>
-    </row>
-    <row r="16" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="20"/>
-      <c r="C16" s="21" t="s">
+      <c r="B15" s="19"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="17"/>
+    </row>
+    <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="19"/>
+      <c r="C16" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="F16" s="18"/>
+      <c r="F16" s="17"/>
     </row>
     <row r="17" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="20"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="17"/>
     </row>
     <row r="18" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/01_proyecto/trim1/01_contextualizacion_proyecto/PL01 - Plantilla de Definición.xlsx
+++ b/01_proyecto/trim1/01_contextualizacion_proyecto/PL01 - Plantilla de Definición.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZUS\Desktop\hola\Innovation_Fusion\01_proyecto\trim1\01_contextualizacion_proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1EEFEB-2C38-4485-9671-A4BD5EDAADB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B9C811-5EA3-4302-95A6-321CEA744663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipo" sheetId="1" r:id="rId1"/>
     <sheet name="Requerimientos" sheetId="2" r:id="rId2"/>
     <sheet name="Diagrama Gantt" sheetId="4" r:id="rId3"/>
     <sheet name="Historia de Usuario" sheetId="3" r:id="rId4"/>
-    <sheet name="Hoja1" sheetId="5" r:id="rId5"/>
+    <sheet name="Gestión de Productos e Inventar" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="184">
   <si>
     <t>#</t>
   </si>
@@ -91,9 +91,6 @@
     <t>Funcional</t>
   </si>
   <si>
-    <t>RE_002</t>
-  </si>
-  <si>
     <t># Requerimiento</t>
   </si>
   <si>
@@ -104,12 +101,6 @@
   </si>
   <si>
     <t>Propósito (Para)</t>
-  </si>
-  <si>
-    <t>HU_001</t>
-  </si>
-  <si>
-    <t>Jefe de Contabilidad</t>
   </si>
   <si>
     <t>Ayudar a los miembros del equipo de cartera en la validación de los estados de cartera de los clientes, actualizar estados de cartera y notificar los clientes con carteras de fechas mas vencidas.</t>
@@ -534,6 +525,66 @@
   </si>
   <si>
     <t>Redactado</t>
+  </si>
+  <si>
+    <t>HU_002</t>
+  </si>
+  <si>
+    <t>RE_003</t>
+  </si>
+  <si>
+    <t>administrador</t>
+  </si>
+  <si>
+    <t>HU_013</t>
+  </si>
+  <si>
+    <t>Administrador</t>
+  </si>
+  <si>
+    <t>Incluir nuevos productos, ver los productos, editar los detalles de los existentes y eliminarlos del catálogo de productos.</t>
+  </si>
+  <si>
+    <t>HU_014</t>
+  </si>
+  <si>
+    <t>HU_015</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> incluir el manejo del stock con las tallas y colores disponibles, ver el stock, editar el stock y eliminarlo </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> para asegurar que la tienda esté actualizada con lo que este en stock</t>
+  </si>
+  <si>
+    <t>HU_013_CA01</t>
+  </si>
+  <si>
+    <t>Interfaz de usuario</t>
+  </si>
+  <si>
+    <t>Campos en BD</t>
+  </si>
+  <si>
+    <t>HU_013_CA02</t>
+  </si>
+  <si>
+    <t>HU_013_CA03</t>
+  </si>
+  <si>
+    <t>El sistema debe realizar las peraciones basicas del crud</t>
+  </si>
+  <si>
+    <t>El sistema debe tener una interfaz donde se vea la gestion de producto</t>
+  </si>
+  <si>
+    <t>El sistema debe tener  una tabla en donde pueda almacenar la informacion de los productos</t>
+  </si>
+  <si>
+    <t>Crud Backend</t>
+  </si>
+  <si>
+    <t>gestionar eficientemente el catálogo de la tienda</t>
   </si>
 </sst>
 </file>
@@ -562,11 +613,6 @@
       <b/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -620,6 +666,11 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -685,7 +736,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -724,74 +775,71 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
+      <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -799,23 +847,54 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
+      <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -823,9 +902,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -836,10 +915,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -848,13 +924,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -865,50 +941,65 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1180,10 +1271,10 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G4" s="2">
         <v>1000100123</v>
@@ -1206,16 +1297,16 @@
         <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2">
         <v>1022351712</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>37</v>
+      <c r="H5" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="I5" s="2">
         <v>3009234567</v>
@@ -1232,10 +1323,10 @@
         <v>13</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2">
         <v>1000100912</v>
@@ -1258,10 +1349,10 @@
         <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7" s="2">
         <v>1000100912</v>
@@ -1284,10 +1375,10 @@
         <v>13</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G8" s="2">
         <v>1000100912</v>
@@ -1310,16 +1401,16 @@
         <v>13</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G9" s="2">
         <v>1022351712</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>37</v>
+      <c r="H9" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="I9" s="2">
         <v>3008234567</v>
@@ -2352,884 +2443,884 @@
     <row r="1" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>39</v>
+      <c r="H3" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+    </row>
+    <row r="5" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-    </row>
-    <row r="5" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="8" t="s">
+      <c r="F5" s="8">
+        <v>5</v>
+      </c>
+      <c r="G5" s="8">
+        <v>3</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="8">
+        <v>5</v>
+      </c>
+      <c r="G6" s="8">
+        <v>7</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="8">
+        <v>5</v>
+      </c>
+      <c r="G7" s="8">
+        <v>7</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="D8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="8">
+        <v>5</v>
+      </c>
+      <c r="G8" s="8">
+        <v>7</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="8">
+        <v>5</v>
+      </c>
+      <c r="G9" s="8">
+        <v>7</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="9">
+      <c r="C11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="8">
         <v>5</v>
       </c>
-      <c r="G5" s="9">
-        <v>3</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="G11" s="8">
+        <v>7</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="10" t="s">
+      <c r="D12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="8">
+        <v>5</v>
+      </c>
+      <c r="G12" s="8">
+        <v>7</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="8">
+        <v>5</v>
+      </c>
+      <c r="G13" s="8">
+        <v>7</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="8">
+        <v>5</v>
+      </c>
+      <c r="G14" s="8">
+        <v>7</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="8">
+        <v>5</v>
+      </c>
+      <c r="G15" s="8">
+        <v>7</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="8">
+        <v>5</v>
+      </c>
+      <c r="G16" s="8">
+        <v>7</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="8">
+        <v>5</v>
+      </c>
+      <c r="G17" s="8">
+        <v>7</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="9">
+      <c r="C19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="8">
         <v>5</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G19" s="8">
         <v>7</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="H19" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="D20" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="8">
         <v>5</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G20" s="8">
         <v>7</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="H20" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="9">
+      <c r="D21" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="8">
         <v>5</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G21" s="8">
         <v>7</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="H21" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+    </row>
+    <row r="23" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D23" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="8">
+        <v>5</v>
+      </c>
+      <c r="G23" s="8">
+        <v>7</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+    </row>
+    <row r="25" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F25" s="8">
+        <v>5</v>
+      </c>
+      <c r="G25" s="8">
+        <v>7</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="8">
+        <v>5</v>
+      </c>
+      <c r="G26" s="8">
+        <v>7</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" s="8">
+        <v>5</v>
+      </c>
+      <c r="G27" s="8">
+        <v>7</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="8">
+        <v>5</v>
+      </c>
+      <c r="G28" s="8">
+        <v>7</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" s="8">
+        <v>5</v>
+      </c>
+      <c r="G29" s="8">
+        <v>7</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="8">
+        <v>5</v>
+      </c>
+      <c r="G30" s="8">
+        <v>7</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F31" s="8">
+        <v>5</v>
+      </c>
+      <c r="G31" s="8">
+        <v>7</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" s="8">
+        <v>5</v>
+      </c>
+      <c r="G32" s="8">
+        <v>7</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="8">
+        <v>5</v>
+      </c>
+      <c r="G33" s="8">
+        <v>7</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+    </row>
+    <row r="35" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="8">
+        <v>5</v>
+      </c>
+      <c r="G35" s="8">
+        <v>7</v>
+      </c>
+      <c r="H35" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="9">
+    </row>
+    <row r="36" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F36" s="8">
         <v>5</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G36" s="8">
         <v>7</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-    </row>
-    <row r="11" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="H36" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="9">
+      <c r="D37" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" s="8">
         <v>5</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G37" s="8">
         <v>7</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="H37" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="9">
+      <c r="D38" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F38" s="8">
         <v>5</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G38" s="8">
         <v>7</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="H38" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+    </row>
+    <row r="40" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="9">
+      <c r="D40" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F40" s="8">
         <v>5</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G40" s="8">
         <v>7</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="H40" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="9">
+      <c r="D41" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F41" s="8">
         <v>5</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G41" s="8">
         <v>7</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="H41" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+    </row>
+    <row r="43" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="9">
+      <c r="D43" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F43" s="8">
         <v>5</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G43" s="8">
         <v>7</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="H43" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+    </row>
+    <row r="45" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" s="9">
+      <c r="D45" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F45" s="8">
         <v>5</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G45" s="8">
         <v>7</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="9">
-        <v>5</v>
-      </c>
-      <c r="G17" s="9">
-        <v>7</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-    </row>
-    <row r="19" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="9">
-        <v>5</v>
-      </c>
-      <c r="G19" s="9">
-        <v>7</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="9">
-        <v>5</v>
-      </c>
-      <c r="G20" s="9">
-        <v>7</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="9">
-        <v>5</v>
-      </c>
-      <c r="G21" s="9">
-        <v>7</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-    </row>
-    <row r="23" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23" s="9">
-        <v>5</v>
-      </c>
-      <c r="G23" s="9">
-        <v>7</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-    </row>
-    <row r="25" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="9">
-        <v>5</v>
-      </c>
-      <c r="G25" s="9">
-        <v>7</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26" s="9">
-        <v>5</v>
-      </c>
-      <c r="G26" s="9">
-        <v>7</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F27" s="9">
-        <v>5</v>
-      </c>
-      <c r="G27" s="9">
-        <v>7</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F28" s="9">
-        <v>5</v>
-      </c>
-      <c r="G28" s="9">
-        <v>7</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F29" s="9">
-        <v>5</v>
-      </c>
-      <c r="G29" s="9">
-        <v>7</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F30" s="9">
-        <v>5</v>
-      </c>
-      <c r="G30" s="9">
-        <v>7</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="F31" s="9">
-        <v>5</v>
-      </c>
-      <c r="G31" s="9">
-        <v>7</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F32" s="9">
-        <v>5</v>
-      </c>
-      <c r="G32" s="9">
-        <v>7</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="F33" s="9">
-        <v>5</v>
-      </c>
-      <c r="G33" s="9">
-        <v>7</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-    </row>
-    <row r="35" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F35" s="9">
-        <v>5</v>
-      </c>
-      <c r="G35" s="9">
-        <v>7</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="F36" s="9">
-        <v>5</v>
-      </c>
-      <c r="G36" s="9">
-        <v>7</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="F37" s="9">
-        <v>5</v>
-      </c>
-      <c r="G37" s="9">
-        <v>7</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="F38" s="9">
-        <v>5</v>
-      </c>
-      <c r="G38" s="9">
-        <v>7</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-    </row>
-    <row r="40" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F40" s="9">
-        <v>5</v>
-      </c>
-      <c r="G40" s="9">
-        <v>7</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F41" s="9">
-        <v>5</v>
-      </c>
-      <c r="G41" s="9">
-        <v>7</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-    </row>
-    <row r="43" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F43" s="9">
-        <v>5</v>
-      </c>
-      <c r="G43" s="9">
-        <v>7</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-    </row>
-    <row r="45" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F45" s="9">
-        <v>5</v>
-      </c>
-      <c r="G45" s="9">
-        <v>7</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>62</v>
+      <c r="H45" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4195,7 +4286,7 @@
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F5:F9 F11:F17 F19:F21 F23 F25:F33 F35:F38 F40:F41 F43 F45" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
@@ -4223,1365 +4314,1365 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="16">
+        <v>45979</v>
+      </c>
+      <c r="E1" s="16">
+        <v>45980</v>
+      </c>
+      <c r="F1" s="16">
+        <v>45981</v>
+      </c>
+      <c r="G1" s="16">
+        <v>45982</v>
+      </c>
+      <c r="H1" s="16">
+        <v>45983</v>
+      </c>
+      <c r="I1" s="16">
+        <v>45984</v>
+      </c>
+      <c r="J1" s="16">
+        <v>45985</v>
+      </c>
+      <c r="K1" s="16">
+        <v>45986</v>
+      </c>
+      <c r="L1" s="16">
+        <v>45987</v>
+      </c>
+      <c r="M1" s="16">
+        <v>45988</v>
+      </c>
+      <c r="N1" s="16">
+        <v>45989</v>
+      </c>
+      <c r="O1" s="16">
+        <v>45990</v>
+      </c>
+      <c r="P1" s="16">
+        <v>45991</v>
+      </c>
+      <c r="Q1" s="16">
+        <v>45992</v>
+      </c>
+      <c r="R1" s="16">
+        <v>45993</v>
+      </c>
+      <c r="S1" s="16">
+        <v>45994</v>
+      </c>
+      <c r="T1" s="16">
+        <v>45995</v>
+      </c>
+      <c r="U1" s="16">
+        <v>45996</v>
+      </c>
+      <c r="V1" s="16">
+        <v>45997</v>
+      </c>
+      <c r="W1" s="16">
+        <v>45998</v>
+      </c>
+      <c r="X1" s="16">
+        <v>45999</v>
+      </c>
+      <c r="Y1" s="16">
+        <v>46000</v>
+      </c>
+      <c r="Z1" s="16">
+        <v>46001</v>
+      </c>
+      <c r="AA1" s="16">
+        <v>46002</v>
+      </c>
+      <c r="AB1" s="16">
+        <v>46003</v>
+      </c>
+      <c r="AC1" s="16">
+        <v>46004</v>
+      </c>
+      <c r="AD1" s="16">
+        <v>46005</v>
+      </c>
+      <c r="AE1" s="16">
+        <v>46006</v>
+      </c>
+      <c r="AF1" s="16">
+        <v>46007</v>
+      </c>
+      <c r="AG1" s="16">
+        <v>46008</v>
+      </c>
+      <c r="AH1" s="16">
+        <v>46009</v>
+      </c>
+      <c r="AI1" s="16">
+        <v>46010</v>
+      </c>
+      <c r="AJ1" s="16">
+        <v>46011</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+    </row>
+    <row r="3" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+    </row>
+    <row r="4" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="10"/>
+      <c r="AG4" s="10"/>
+    </row>
+    <row r="5" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="10"/>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+    </row>
+    <row r="6" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
+      <c r="AA6" s="10"/>
+      <c r="AB6" s="10"/>
+      <c r="AC6" s="10"/>
+      <c r="AD6" s="10"/>
+      <c r="AE6" s="10"/>
+      <c r="AF6" s="10"/>
+      <c r="AG6" s="10"/>
+    </row>
+    <row r="7" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
+      <c r="AC7" s="10"/>
+      <c r="AD7" s="10"/>
+      <c r="AE7" s="10"/>
+      <c r="AF7" s="10"/>
+      <c r="AG7" s="10"/>
+    </row>
+    <row r="8" spans="1:36" ht="57" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="10"/>
+      <c r="AB8" s="10"/>
+      <c r="AC8" s="10"/>
+      <c r="AD8" s="10"/>
+      <c r="AE8" s="10"/>
+      <c r="AF8" s="10"/>
+      <c r="AG8" s="10"/>
+    </row>
+    <row r="9" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="10"/>
+      <c r="AA9" s="10"/>
+      <c r="AB9" s="10"/>
+      <c r="AC9" s="10"/>
+      <c r="AD9" s="10"/>
+      <c r="AE9" s="10"/>
+      <c r="AF9" s="10"/>
+      <c r="AG9" s="10"/>
+    </row>
+    <row r="10" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="10"/>
+    </row>
+    <row r="11" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="10"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+      <c r="AE11" s="10"/>
+      <c r="AF11" s="10"/>
+      <c r="AG11" s="10"/>
+    </row>
+    <row r="12" spans="1:36" ht="57" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="10"/>
+      <c r="AF12" s="10"/>
+      <c r="AG12" s="10"/>
+    </row>
+    <row r="13" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="10"/>
+      <c r="AC13" s="10"/>
+      <c r="AD13" s="10"/>
+      <c r="AE13" s="10"/>
+      <c r="AF13" s="10"/>
+      <c r="AG13" s="10"/>
+    </row>
+    <row r="14" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="16">
+        <v>39583</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="10"/>
+      <c r="AB14" s="10"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
+      <c r="AF14" s="10"/>
+      <c r="AG14" s="10"/>
+    </row>
+    <row r="15" spans="1:36" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
+      <c r="AD15" s="10"/>
+      <c r="AE15" s="10"/>
+      <c r="AF15" s="10"/>
+      <c r="AG15" s="10"/>
+    </row>
+    <row r="16" spans="1:36" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="10"/>
+      <c r="AF16" s="10"/>
+      <c r="AG16" s="10"/>
+    </row>
+    <row r="17" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="10"/>
+      <c r="AB17" s="10"/>
+      <c r="AC17" s="10"/>
+      <c r="AD17" s="10"/>
+      <c r="AE17" s="10"/>
+      <c r="AF17" s="10"/>
+      <c r="AG17" s="10"/>
+    </row>
+    <row r="18" spans="1:33" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="10"/>
+      <c r="AF18" s="10"/>
+      <c r="AG18" s="10"/>
+    </row>
+    <row r="19" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
+      <c r="AC19" s="10"/>
+      <c r="AD19" s="10"/>
+      <c r="AE19" s="10"/>
+      <c r="AF19" s="10"/>
+      <c r="AG19" s="10"/>
+    </row>
+    <row r="20" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
+      <c r="AD20" s="10"/>
+      <c r="AE20" s="10"/>
+      <c r="AF20" s="10"/>
+      <c r="AG20" s="10"/>
+    </row>
+    <row r="21" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
+      <c r="AD21" s="10"/>
+      <c r="AE21" s="10"/>
+      <c r="AF21" s="10"/>
+      <c r="AG21" s="10"/>
+    </row>
+    <row r="22" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
+      <c r="Z22" s="10"/>
+      <c r="AA22" s="10"/>
+      <c r="AB22" s="10"/>
+      <c r="AC22" s="10"/>
+      <c r="AD22" s="10"/>
+      <c r="AE22" s="10"/>
+      <c r="AF22" s="10"/>
+      <c r="AG22" s="10"/>
+    </row>
+    <row r="23" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
+      <c r="AA23" s="10"/>
+      <c r="AB23" s="10"/>
+      <c r="AC23" s="10"/>
+      <c r="AD23" s="10"/>
+      <c r="AE23" s="10"/>
+      <c r="AF23" s="10"/>
+      <c r="AG23" s="10"/>
+    </row>
+    <row r="24" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+      <c r="AA24" s="10"/>
+      <c r="AB24" s="10"/>
+      <c r="AC24" s="10"/>
+      <c r="AD24" s="10"/>
+      <c r="AE24" s="10"/>
+      <c r="AF24" s="10"/>
+      <c r="AG24" s="10"/>
+    </row>
+    <row r="25" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="10"/>
+      <c r="Z25" s="10"/>
+      <c r="AA25" s="10"/>
+      <c r="AB25" s="10"/>
+      <c r="AC25" s="10"/>
+      <c r="AD25" s="10"/>
+      <c r="AE25" s="10"/>
+      <c r="AF25" s="10"/>
+      <c r="AG25" s="10"/>
+    </row>
+    <row r="26" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="10"/>
+      <c r="Y26" s="10"/>
+      <c r="Z26" s="10"/>
+      <c r="AA26" s="10"/>
+      <c r="AB26" s="10"/>
+      <c r="AC26" s="10"/>
+      <c r="AD26" s="10"/>
+      <c r="AE26" s="10"/>
+      <c r="AF26" s="10"/>
+      <c r="AG26" s="10"/>
+    </row>
+    <row r="27" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
+      <c r="V27" s="10"/>
+      <c r="W27" s="10"/>
+      <c r="X27" s="10"/>
+      <c r="Y27" s="10"/>
+      <c r="Z27" s="10"/>
+      <c r="AA27" s="10"/>
+      <c r="AB27" s="10"/>
+      <c r="AC27" s="10"/>
+      <c r="AD27" s="10"/>
+      <c r="AE27" s="10"/>
+      <c r="AF27" s="10"/>
+      <c r="AG27" s="10"/>
+    </row>
+    <row r="28" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10"/>
+      <c r="V28" s="10"/>
+      <c r="W28" s="10"/>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="10"/>
+      <c r="Z28" s="10"/>
+      <c r="AA28" s="10"/>
+      <c r="AB28" s="10"/>
+      <c r="AC28" s="10"/>
+      <c r="AD28" s="10"/>
+      <c r="AE28" s="10"/>
+      <c r="AF28" s="10"/>
+      <c r="AG28" s="10"/>
+    </row>
+    <row r="29" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
+      <c r="Z29" s="10"/>
+      <c r="AA29" s="10"/>
+      <c r="AB29" s="10"/>
+      <c r="AC29" s="10"/>
+      <c r="AD29" s="10"/>
+      <c r="AE29" s="10"/>
+      <c r="AF29" s="10"/>
+      <c r="AG29" s="10"/>
+    </row>
+    <row r="30" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
+      <c r="AA30" s="10"/>
+      <c r="AB30" s="10"/>
+      <c r="AC30" s="10"/>
+      <c r="AD30" s="10"/>
+      <c r="AE30" s="10"/>
+      <c r="AF30" s="10"/>
+      <c r="AG30" s="10"/>
+    </row>
+    <row r="31" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
+      <c r="V31" s="10"/>
+      <c r="W31" s="10"/>
+      <c r="X31" s="10"/>
+      <c r="Y31" s="10"/>
+      <c r="Z31" s="10"/>
+      <c r="AA31" s="10"/>
+      <c r="AB31" s="10"/>
+      <c r="AC31" s="10"/>
+      <c r="AD31" s="10"/>
+      <c r="AE31" s="10"/>
+      <c r="AF31" s="10"/>
+      <c r="AG31" s="10"/>
+    </row>
+    <row r="32" spans="1:33" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10"/>
+      <c r="U32" s="10"/>
+      <c r="V32" s="10"/>
+      <c r="W32" s="10"/>
+      <c r="X32" s="10"/>
+      <c r="Y32" s="10"/>
+      <c r="Z32" s="10"/>
+      <c r="AA32" s="10"/>
+      <c r="AB32" s="10"/>
+      <c r="AC32" s="10"/>
+      <c r="AD32" s="10"/>
+      <c r="AE32" s="10"/>
+      <c r="AF32" s="10"/>
+      <c r="AG32" s="10"/>
+    </row>
+    <row r="33" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
+      <c r="AA33" s="10"/>
+      <c r="AB33" s="10"/>
+      <c r="AC33" s="10"/>
+      <c r="AD33" s="10"/>
+      <c r="AE33" s="10"/>
+      <c r="AF33" s="10"/>
+      <c r="AG33" s="10"/>
+    </row>
+    <row r="34" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
+      <c r="X34" s="10"/>
+      <c r="Y34" s="10"/>
+      <c r="Z34" s="10"/>
+      <c r="AA34" s="10"/>
+      <c r="AB34" s="10"/>
+      <c r="AC34" s="10"/>
+      <c r="AD34" s="10"/>
+      <c r="AE34" s="10"/>
+      <c r="AF34" s="10"/>
+      <c r="AG34" s="10"/>
+    </row>
+    <row r="36" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="E36" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F36" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="31">
-        <v>45979</v>
-      </c>
-      <c r="E1" s="31">
-        <v>45980</v>
-      </c>
-      <c r="F1" s="31">
-        <v>45981</v>
-      </c>
-      <c r="G1" s="31">
-        <v>45982</v>
-      </c>
-      <c r="H1" s="31">
-        <v>45983</v>
-      </c>
-      <c r="I1" s="31">
-        <v>45984</v>
-      </c>
-      <c r="J1" s="31">
-        <v>45985</v>
-      </c>
-      <c r="K1" s="31">
-        <v>45986</v>
-      </c>
-      <c r="L1" s="31">
-        <v>45987</v>
-      </c>
-      <c r="M1" s="31">
-        <v>45988</v>
-      </c>
-      <c r="N1" s="31">
-        <v>45989</v>
-      </c>
-      <c r="O1" s="31">
-        <v>45990</v>
-      </c>
-      <c r="P1" s="31">
-        <v>45991</v>
-      </c>
-      <c r="Q1" s="31">
-        <v>45992</v>
-      </c>
-      <c r="R1" s="31">
-        <v>45993</v>
-      </c>
-      <c r="S1" s="31">
-        <v>45994</v>
-      </c>
-      <c r="T1" s="31">
-        <v>45995</v>
-      </c>
-      <c r="U1" s="31">
-        <v>45996</v>
-      </c>
-      <c r="V1" s="31">
-        <v>45997</v>
-      </c>
-      <c r="W1" s="31">
-        <v>45998</v>
-      </c>
-      <c r="X1" s="31">
-        <v>45999</v>
-      </c>
-      <c r="Y1" s="31">
-        <v>46000</v>
-      </c>
-      <c r="Z1" s="31">
-        <v>46001</v>
-      </c>
-      <c r="AA1" s="31">
-        <v>46002</v>
-      </c>
-      <c r="AB1" s="31">
-        <v>46003</v>
-      </c>
-      <c r="AC1" s="31">
-        <v>46004</v>
-      </c>
-      <c r="AD1" s="31">
-        <v>46005</v>
-      </c>
-      <c r="AE1" s="31">
-        <v>46006</v>
-      </c>
-      <c r="AF1" s="31">
-        <v>46007</v>
-      </c>
-      <c r="AG1" s="31">
-        <v>46008</v>
-      </c>
-      <c r="AH1" s="31">
-        <v>46009</v>
-      </c>
-      <c r="AI1" s="31">
-        <v>46010</v>
-      </c>
-      <c r="AJ1" s="31">
-        <v>46011</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-    </row>
-    <row r="3" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="11"/>
-      <c r="AA3" s="11"/>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="11"/>
-      <c r="AD3" s="11"/>
-      <c r="AE3" s="11"/>
-      <c r="AF3" s="11"/>
-      <c r="AG3" s="11"/>
-    </row>
-    <row r="4" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="11"/>
-      <c r="AA4" s="11"/>
-      <c r="AB4" s="11"/>
-      <c r="AC4" s="11"/>
-      <c r="AD4" s="11"/>
-      <c r="AE4" s="11"/>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="11"/>
-    </row>
-    <row r="5" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="11"/>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="11"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11"/>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="11"/>
-      <c r="AG5" s="11"/>
-    </row>
-    <row r="6" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="11"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="11"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="11"/>
-      <c r="AF6" s="11"/>
-      <c r="AG6" s="11"/>
-    </row>
-    <row r="7" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="11"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="11"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="11"/>
-      <c r="AG7" s="11"/>
-    </row>
-    <row r="8" spans="1:36" ht="57" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="11"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="11"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="11"/>
-      <c r="AG8" s="11"/>
-    </row>
-    <row r="9" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="11"/>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="11"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="11"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="11"/>
-      <c r="AG9" s="11"/>
-    </row>
-    <row r="10" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="11"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="11"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="11"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="11"/>
-      <c r="AG10" s="11"/>
-    </row>
-    <row r="11" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="11"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="11"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="11"/>
-      <c r="AG11" s="11"/>
-    </row>
-    <row r="12" spans="1:36" ht="57" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="11"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="11"/>
-      <c r="AG12" s="11"/>
-    </row>
-    <row r="13" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="11"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="11"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="11"/>
-      <c r="AG13" s="11"/>
-    </row>
-    <row r="14" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="31">
-        <v>39583</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="11"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="11"/>
-      <c r="AG14" s="11"/>
-    </row>
-    <row r="15" spans="1:36" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="11"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="11"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="11"/>
-      <c r="AG15" s="11"/>
-    </row>
-    <row r="16" spans="1:36" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="11"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="11"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="11"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="11"/>
-      <c r="AF16" s="11"/>
-      <c r="AG16" s="11"/>
-    </row>
-    <row r="17" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="11"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="11"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="11"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="11"/>
-      <c r="AF17" s="11"/>
-      <c r="AG17" s="11"/>
-    </row>
-    <row r="18" spans="1:33" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="11"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="11"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="11"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="11"/>
-      <c r="AF18" s="11"/>
-      <c r="AG18" s="11"/>
-    </row>
-    <row r="19" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="11"/>
-      <c r="AG19" s="11"/>
-    </row>
-    <row r="20" spans="1:33" ht="57" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="11"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="11"/>
-      <c r="AG20" s="11"/>
-    </row>
-    <row r="21" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="11"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="11"/>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="11"/>
-      <c r="AB21" s="11"/>
-      <c r="AC21" s="11"/>
-      <c r="AD21" s="11"/>
-      <c r="AE21" s="11"/>
-      <c r="AF21" s="11"/>
-      <c r="AG21" s="11"/>
-    </row>
-    <row r="22" spans="1:33" ht="57" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="11"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="11"/>
-      <c r="AD22" s="11"/>
-      <c r="AE22" s="11"/>
-      <c r="AF22" s="11"/>
-      <c r="AG22" s="11"/>
-    </row>
-    <row r="23" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="11"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="11"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="11"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="11"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="11"/>
-      <c r="AD23" s="11"/>
-      <c r="AE23" s="11"/>
-      <c r="AF23" s="11"/>
-      <c r="AG23" s="11"/>
-    </row>
-    <row r="24" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="11"/>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="11"/>
-      <c r="AB24" s="11"/>
-      <c r="AC24" s="11"/>
-      <c r="AD24" s="11"/>
-      <c r="AE24" s="11"/>
-      <c r="AF24" s="11"/>
-      <c r="AG24" s="11"/>
-    </row>
-    <row r="25" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="11"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="11"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="11"/>
-      <c r="AB25" s="11"/>
-      <c r="AC25" s="11"/>
-      <c r="AD25" s="11"/>
-      <c r="AE25" s="11"/>
-      <c r="AF25" s="11"/>
-      <c r="AG25" s="11"/>
-    </row>
-    <row r="26" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="11"/>
-      <c r="V26" s="11"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="11"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="11"/>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="11"/>
-      <c r="AD26" s="11"/>
-      <c r="AE26" s="11"/>
-      <c r="AF26" s="11"/>
-      <c r="AG26" s="11"/>
-    </row>
-    <row r="27" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A27" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="11"/>
-      <c r="S27" s="11"/>
-      <c r="T27" s="11"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="11"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="11"/>
-      <c r="Z27" s="11"/>
-      <c r="AA27" s="11"/>
-      <c r="AB27" s="11"/>
-      <c r="AC27" s="11"/>
-      <c r="AD27" s="11"/>
-      <c r="AE27" s="11"/>
-      <c r="AF27" s="11"/>
-      <c r="AG27" s="11"/>
-    </row>
-    <row r="28" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="11"/>
-      <c r="S28" s="11"/>
-      <c r="T28" s="11"/>
-      <c r="U28" s="11"/>
-      <c r="V28" s="11"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="11"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="11"/>
-      <c r="AB28" s="11"/>
-      <c r="AC28" s="11"/>
-      <c r="AD28" s="11"/>
-      <c r="AE28" s="11"/>
-      <c r="AF28" s="11"/>
-      <c r="AG28" s="11"/>
-    </row>
-    <row r="29" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
-      <c r="S29" s="11"/>
-      <c r="T29" s="11"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="11"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="11"/>
-      <c r="Z29" s="11"/>
-      <c r="AA29" s="11"/>
-      <c r="AB29" s="11"/>
-      <c r="AC29" s="11"/>
-      <c r="AD29" s="11"/>
-      <c r="AE29" s="11"/>
-      <c r="AF29" s="11"/>
-      <c r="AG29" s="11"/>
-    </row>
-    <row r="30" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="11"/>
-      <c r="T30" s="11"/>
-      <c r="U30" s="11"/>
-      <c r="V30" s="11"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="11"/>
-      <c r="Z30" s="11"/>
-      <c r="AA30" s="11"/>
-      <c r="AB30" s="11"/>
-      <c r="AC30" s="11"/>
-      <c r="AD30" s="11"/>
-      <c r="AE30" s="11"/>
-      <c r="AF30" s="11"/>
-      <c r="AG30" s="11"/>
-    </row>
-    <row r="31" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="11"/>
-      <c r="S31" s="11"/>
-      <c r="T31" s="11"/>
-      <c r="U31" s="11"/>
-      <c r="V31" s="11"/>
-      <c r="W31" s="11"/>
-      <c r="X31" s="11"/>
-      <c r="Y31" s="11"/>
-      <c r="Z31" s="11"/>
-      <c r="AA31" s="11"/>
-      <c r="AB31" s="11"/>
-      <c r="AC31" s="11"/>
-      <c r="AD31" s="11"/>
-      <c r="AE31" s="11"/>
-      <c r="AF31" s="11"/>
-      <c r="AG31" s="11"/>
-    </row>
-    <row r="32" spans="1:33" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-      <c r="R32" s="11"/>
-      <c r="S32" s="11"/>
-      <c r="T32" s="11"/>
-      <c r="U32" s="11"/>
-      <c r="V32" s="11"/>
-      <c r="W32" s="11"/>
-      <c r="X32" s="11"/>
-      <c r="Y32" s="11"/>
-      <c r="Z32" s="11"/>
-      <c r="AA32" s="11"/>
-      <c r="AB32" s="11"/>
-      <c r="AC32" s="11"/>
-      <c r="AD32" s="11"/>
-      <c r="AE32" s="11"/>
-      <c r="AF32" s="11"/>
-      <c r="AG32" s="11"/>
-    </row>
-    <row r="33" spans="1:33" ht="57" x14ac:dyDescent="0.2">
-      <c r="A33" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-      <c r="R33" s="11"/>
-      <c r="S33" s="11"/>
-      <c r="T33" s="11"/>
-      <c r="U33" s="11"/>
-      <c r="V33" s="11"/>
-      <c r="W33" s="11"/>
-      <c r="X33" s="11"/>
-      <c r="Y33" s="11"/>
-      <c r="Z33" s="11"/>
-      <c r="AA33" s="11"/>
-      <c r="AB33" s="11"/>
-      <c r="AC33" s="11"/>
-      <c r="AD33" s="11"/>
-      <c r="AE33" s="11"/>
-      <c r="AF33" s="11"/>
-      <c r="AG33" s="11"/>
-    </row>
-    <row r="34" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A34" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="11"/>
-      <c r="R34" s="11"/>
-      <c r="S34" s="11"/>
-      <c r="T34" s="11"/>
-      <c r="U34" s="11"/>
-      <c r="V34" s="11"/>
-      <c r="W34" s="11"/>
-      <c r="X34" s="11"/>
-      <c r="Y34" s="11"/>
-      <c r="Z34" s="11"/>
-      <c r="AA34" s="11"/>
-      <c r="AB34" s="11"/>
-      <c r="AC34" s="11"/>
-      <c r="AD34" s="11"/>
-      <c r="AE34" s="11"/>
-      <c r="AF34" s="11"/>
-      <c r="AG34" s="11"/>
-    </row>
-    <row r="36" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="E36" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>88</v>
+      <c r="G36" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="E37" s="11"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="14"/>
-    </row>
-    <row r="38" spans="1:33" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="B38" s="6" t="s">
-        <v>38</v>
+      <c r="E37" s="10"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="13"/>
+    </row>
+    <row r="38" spans="1:33" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B38" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -5594,7 +5685,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B1:F1000"/>
+  <dimension ref="B1:F995"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -5612,149 +5703,757 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="1" t="s">
+    </row>
+    <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21"/>
+    </row>
+    <row r="5" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" ht="86.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="2" t="s">
+      <c r="F5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="6" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="2"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="35"/>
+    </row>
+    <row r="17" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="29" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="35"/>
+    </row>
+    <row r="41" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+    </row>
+    <row r="51" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+    </row>
+    <row r="52" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+    </row>
+    <row r="53" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+    </row>
+    <row r="54" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="35"/>
+    </row>
+    <row r="55" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+    </row>
+    <row r="57" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+    </row>
+    <row r="60" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+    </row>
+    <row r="64" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+    </row>
+    <row r="67" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+    </row>
+    <row r="68" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="35"/>
+    </row>
+    <row r="70" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+    </row>
+    <row r="72" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+    </row>
+    <row r="73" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+    </row>
+    <row r="74" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+    </row>
+    <row r="75" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+    </row>
+    <row r="76" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+    </row>
+    <row r="77" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+    </row>
+    <row r="78" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+    </row>
+    <row r="79" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+    </row>
+    <row r="80" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+    </row>
+    <row r="81" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+    </row>
+    <row r="82" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C82" s="32"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="32"/>
+      <c r="F82" s="35"/>
+    </row>
+    <row r="83" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+    </row>
+    <row r="84" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+    </row>
+    <row r="85" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+    </row>
+    <row r="86" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+    </row>
+    <row r="87" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+    </row>
+    <row r="88" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+    </row>
+    <row r="89" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+    </row>
+    <row r="90" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+    </row>
+    <row r="91" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+    </row>
+    <row r="92" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+    </row>
+    <row r="93" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="C93" s="32"/>
+      <c r="D93" s="32"/>
+      <c r="E93" s="32"/>
+      <c r="F93" s="35"/>
+    </row>
+    <row r="94" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+    </row>
+    <row r="95" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+    </row>
+    <row r="96" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+    </row>
+    <row r="97" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+    </row>
+    <row r="98" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+    </row>
+    <row r="99" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+    </row>
+    <row r="100" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6638,24 +7337,26 @@
     <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Auxiliar Contable,Auxiliar Administrativo,Jefe de Contabilidad"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <mergeCells count="9">
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B16:F16"/>
+  </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D2BA1A-E3EC-4B05-B9AB-FCC72E25559E}">
-  <dimension ref="B2:F18"/>
+  <dimension ref="C4:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3.85546875" customWidth="1"/>
@@ -6664,150 +7365,131 @@
     <col min="5" max="5" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="17"/>
-    </row>
-    <row r="4" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="19"/>
-      <c r="C4" s="20" t="s">
+    <row r="4" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C4" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C5" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="25"/>
+    </row>
+    <row r="6" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+    </row>
+    <row r="7" spans="3:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+    </row>
+    <row r="8" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C8" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D8" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E8" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="17"/>
-    </row>
-    <row r="5" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="17"/>
-    </row>
-    <row r="6" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="19"/>
-      <c r="C6" s="25" t="s">
+    </row>
+    <row r="9" spans="3:5" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C9" s="28">
+        <v>5</v>
+      </c>
+      <c r="D9" s="28">
+        <v>8</v>
+      </c>
+      <c r="E9" s="25"/>
+    </row>
+    <row r="10" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C10" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C11" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="17"/>
-    </row>
-    <row r="7" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="19"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="17"/>
-    </row>
-    <row r="8" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="19"/>
-      <c r="C8" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="20" t="s">
+      <c r="E11" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="E8" s="20" t="s">
+    </row>
+    <row r="12" spans="3:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C12" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C13" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="C14" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+    </row>
+    <row r="16" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C16" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="17"/>
-    </row>
-    <row r="9" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="19"/>
-      <c r="C9" s="22">
-        <v>5</v>
-      </c>
-      <c r="D9" s="22">
-        <v>5</v>
-      </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="17"/>
-    </row>
-    <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="19"/>
-      <c r="C10" s="25" t="s">
+      <c r="D16" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="17"/>
-    </row>
-    <row r="11" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="19"/>
-      <c r="C11" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="F11" s="17"/>
-    </row>
-    <row r="12" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="19"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="17"/>
-    </row>
-    <row r="13" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="19"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="17"/>
-    </row>
-    <row r="14" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="19"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="17"/>
-    </row>
-    <row r="15" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="19"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="17"/>
-    </row>
-    <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="19"/>
-      <c r="C16" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16" s="17"/>
-    </row>
-    <row r="17" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="19"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="17"/>
-    </row>
-    <row r="18" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="E16" s="24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6815,6 +7497,7 @@
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="C10:E10"/>
   </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/01_proyecto/trim1/01_contextualizacion_proyecto/PL01 - Plantilla de Definición.xlsx
+++ b/01_proyecto/trim1/01_contextualizacion_proyecto/PL01 - Plantilla de Definición.xlsx
@@ -5,31 +5,33 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZUS\Desktop\hola\Innovation_Fusion\01_proyecto\trim1\01_contextualizacion_proyecto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZUS\Desktop\Innovation_Fusion\01_proyecto\trim1\01_contextualizacion_proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B9C811-5EA3-4302-95A6-321CEA744663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D567C68D-F887-48A1-B4A1-10AB391C5899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="2355" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipo" sheetId="1" r:id="rId1"/>
     <sheet name="Requerimientos" sheetId="2" r:id="rId2"/>
     <sheet name="Diagrama Gantt" sheetId="4" r:id="rId3"/>
     <sheet name="Historia de Usuario" sheetId="3" r:id="rId4"/>
-    <sheet name="Gestión de Productos e Inventar" sheetId="5" r:id="rId5"/>
+    <sheet name="Gestión de Usuarios y Autentica" sheetId="6" r:id="rId5"/>
+    <sheet name="Gestión de Productos e Inve (2)" sheetId="7" r:id="rId6"/>
+    <sheet name="Gestión de Productos e Inventar" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="+CJhT1B5jpkQwxSTxyNLk1YCzpn9UEauZYMdiwIpMNk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="+CJhT1B5jpkQwxSTxyNLk1YCzpn9UEauZYMdiwIpMNk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="187">
   <si>
     <t>#</t>
   </si>
@@ -585,6 +587,15 @@
   </si>
   <si>
     <t>gestionar eficientemente el catálogo de la tienda</t>
+  </si>
+  <si>
+    <t>HU_013_CA04</t>
+  </si>
+  <si>
+    <t>Conexión Api-Frontend</t>
+  </si>
+  <si>
+    <t>El sistema debe tene una conexión de api con frontend</t>
   </si>
 </sst>
 </file>
@@ -943,29 +954,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -982,10 +975,25 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -994,11 +1002,14 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2466,15 +2477,15 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
     </row>
     <row r="5" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -2592,15 +2603,15 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
     </row>
     <row r="11" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="7" t="s">
@@ -2764,15 +2775,15 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
     </row>
     <row r="19" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="8" t="s">
@@ -2844,15 +2855,15 @@
       </c>
     </row>
     <row r="22" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
     </row>
     <row r="23" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -2878,15 +2889,15 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
     </row>
     <row r="25" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="8" t="s">
@@ -3096,15 +3107,15 @@
       </c>
     </row>
     <row r="34" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
     </row>
     <row r="35" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="8" t="s">
@@ -3199,15 +3210,15 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
     </row>
     <row r="40" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="8" t="s">
@@ -3256,15 +3267,15 @@
       </c>
     </row>
     <row r="42" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
     </row>
     <row r="43" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="8" t="s">
@@ -3290,15 +3301,15 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
     </row>
     <row r="45" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="8" t="s">
@@ -5017,7 +5028,7 @@
       <c r="AF17" s="10"/>
       <c r="AG17" s="10"/>
     </row>
-    <row r="18" spans="1:33" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>98</v>
       </c>
@@ -5716,16 +5727,16 @@
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="31"/>
     </row>
     <row r="5" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>164</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -5743,9 +5754,9 @@
     </row>
     <row r="6" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5812,13 +5823,13 @@
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="35"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="28"/>
     </row>
     <row r="17" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
@@ -5870,16 +5881,16 @@
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
     </row>
     <row r="25" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="18" t="s">
         <v>167</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -5896,7 +5907,7 @@
       </c>
     </row>
     <row r="26" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="18" t="s">
         <v>170</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -5913,7 +5924,7 @@
       </c>
     </row>
     <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="18" t="s">
         <v>171</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -5926,13 +5937,13 @@
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="36"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="34"/>
     </row>
     <row r="29" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="2"/>
@@ -6012,13 +6023,13 @@
       <c r="F39" s="2"/>
     </row>
     <row r="40" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="35"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="28"/>
     </row>
     <row r="41" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="2"/>
@@ -6112,13 +6123,13 @@
       <c r="F53" s="2"/>
     </row>
     <row r="54" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="31" t="s">
+      <c r="B54" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="35"/>
+      <c r="C54" s="27"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="28"/>
     </row>
     <row r="55" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="2"/>
@@ -6219,13 +6230,13 @@
       <c r="F68" s="2"/>
     </row>
     <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="31" t="s">
+      <c r="B69" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="C69" s="32"/>
-      <c r="D69" s="32"/>
-      <c r="E69" s="32"/>
-      <c r="F69" s="35"/>
+      <c r="C69" s="27"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="28"/>
     </row>
     <row r="70" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="2"/>
@@ -6312,13 +6323,13 @@
       <c r="F81" s="2"/>
     </row>
     <row r="82" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="31" t="s">
+      <c r="B82" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="C82" s="32"/>
-      <c r="D82" s="32"/>
-      <c r="E82" s="32"/>
-      <c r="F82" s="35"/>
+      <c r="C82" s="27"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="28"/>
     </row>
     <row r="83" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="2"/>
@@ -6391,13 +6402,13 @@
       <c r="F92" s="2"/>
     </row>
     <row r="93" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B93" s="31" t="s">
+      <c r="B93" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="C93" s="32"/>
-      <c r="D93" s="32"/>
-      <c r="E93" s="32"/>
-      <c r="F93" s="35"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="28"/>
     </row>
     <row r="94" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="2"/>
@@ -7355,6 +7366,307 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E79EAF51-6346-4E0C-850A-7884848EE0FC}">
+  <dimension ref="C4:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C4" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C5" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="21"/>
+    </row>
+    <row r="6" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C6" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+    </row>
+    <row r="7" spans="3:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+    </row>
+    <row r="8" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C8" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C9" s="22">
+        <v>5</v>
+      </c>
+      <c r="D9" s="22">
+        <v>8</v>
+      </c>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C10" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C11" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C12" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C13" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="C14" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C15" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C16" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C10:E10"/>
+  </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E03081-6D4B-48F0-9762-CB959C944999}">
+  <dimension ref="C4:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C4" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C5" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="21"/>
+    </row>
+    <row r="6" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C6" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+    </row>
+    <row r="7" spans="3:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+    </row>
+    <row r="8" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C8" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C9" s="22">
+        <v>5</v>
+      </c>
+      <c r="D9" s="22">
+        <v>8</v>
+      </c>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C10" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C11" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C12" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C13" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="C14" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+    </row>
+    <row r="16" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C16" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C10:E10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D2BA1A-E3EC-4B05-B9AB-FCC72E25559E}">
   <dimension ref="C4:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -7366,130 +7678,136 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="20" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
     </row>
     <row r="7" spans="3:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
     </row>
     <row r="8" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="20" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="9" spans="3:5" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C9" s="28">
+      <c r="C9" s="22">
         <v>5</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="22">
         <v>8</v>
       </c>
-      <c r="E9" s="25"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
     </row>
     <row r="11" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="23" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="12" spans="3:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="21" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="13" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="21" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="14" spans="3:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="21" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+    <row r="15" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C15" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="16" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="20" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/01_proyecto/trim1/01_contextualizacion_proyecto/PL01 - Plantilla de Definición.xlsx
+++ b/01_proyecto/trim1/01_contextualizacion_proyecto/PL01 - Plantilla de Definición.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZUS\Desktop\Innovation_Fusion\01_proyecto\trim1\01_contextualizacion_proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D567C68D-F887-48A1-B4A1-10AB391C5899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350B04CA-0AD3-43B7-BCBA-29F0D2C06655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="2355" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipo" sheetId="1" r:id="rId1"/>
     <sheet name="Requerimientos" sheetId="2" r:id="rId2"/>
-    <sheet name="Diagrama Gantt" sheetId="4" r:id="rId3"/>
-    <sheet name="Historia de Usuario" sheetId="3" r:id="rId4"/>
-    <sheet name="Gestión de Usuarios y Autentica" sheetId="6" r:id="rId5"/>
-    <sheet name="Gestión de Productos e Inve (2)" sheetId="7" r:id="rId6"/>
-    <sheet name="Gestión de Productos e Inventar" sheetId="5" r:id="rId7"/>
+    <sheet name="Historia de Usuario" sheetId="3" r:id="rId3"/>
+    <sheet name="Gestión de Usuarios y Autentica" sheetId="6" r:id="rId4"/>
+    <sheet name="Catálogo y Experiencia de Naveg" sheetId="7" r:id="rId5"/>
+    <sheet name="Gestión de Productos e Inventar" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="185">
   <si>
     <t>#</t>
   </si>
@@ -138,19 +137,7 @@
     <t>katherinquiroga18@gmail.com</t>
   </si>
   <si>
-    <t>Nota:Las siguientes fechas se tomaran desde Tests</t>
-  </si>
-  <si>
     <t>Responsable</t>
-  </si>
-  <si>
-    <t>Nombre Actividad</t>
-  </si>
-  <si>
-    <t>Inicio</t>
-  </si>
-  <si>
-    <t>Fin</t>
   </si>
   <si>
     <t>Registrar nuevos usuarios</t>
@@ -496,9 +483,6 @@
     <t>El sistema permitirá obtener información sobre las ventas, lo permitirá tener una previsualización, se podrá genera pdf y excel</t>
   </si>
   <si>
-    <t>Responsables</t>
-  </si>
-  <si>
     <t>Código</t>
   </si>
   <si>
@@ -596,6 +580,15 @@
   </si>
   <si>
     <t>El sistema debe tene una conexión de api con frontend</t>
+  </si>
+  <si>
+    <t>Gestionar Registrar nuevos usuarios</t>
+  </si>
+  <si>
+    <t>HU_001</t>
+  </si>
+  <si>
+    <t>HU_003</t>
   </si>
 </sst>
 </file>
@@ -685,7 +678,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -706,30 +699,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF4A86E8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -737,12 +706,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA4C2F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -915,7 +878,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -929,9 +892,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -944,23 +904,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -969,7 +919,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1005,10 +955,13 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2454,884 +2407,884 @@
     <row r="1" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="25" t="s">
+      <c r="E5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="7">
+        <v>5</v>
+      </c>
+      <c r="G5" s="7">
+        <v>3</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="7">
+        <v>5</v>
+      </c>
+      <c r="G6" s="7">
+        <v>7</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="7">
+        <v>5</v>
+      </c>
+      <c r="G7" s="7">
+        <v>7</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-    </row>
-    <row r="5" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="7" t="s">
+      <c r="F8" s="7">
+        <v>5</v>
+      </c>
+      <c r="G8" s="7">
+        <v>7</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="D9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="7">
+        <v>5</v>
+      </c>
+      <c r="G9" s="7">
+        <v>7</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F11" s="7">
         <v>5</v>
       </c>
-      <c r="G5" s="8">
-        <v>3</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="G11" s="7">
+        <v>7</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="D12" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="7">
+        <v>5</v>
+      </c>
+      <c r="G12" s="7">
+        <v>7</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="7">
+        <v>5</v>
+      </c>
+      <c r="G13" s="7">
+        <v>7</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="7">
+        <v>5</v>
+      </c>
+      <c r="G14" s="7">
+        <v>7</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="7">
+        <v>5</v>
+      </c>
+      <c r="G15" s="7">
+        <v>7</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="7">
+        <v>5</v>
+      </c>
+      <c r="G16" s="7">
+        <v>7</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="7">
+        <v>5</v>
+      </c>
+      <c r="G17" s="7">
+        <v>7</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+    </row>
+    <row r="19" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="8">
+      <c r="E19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="7">
         <v>5</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G19" s="7">
         <v>7</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="H19" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7" s="8">
+      <c r="D20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="7">
         <v>5</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G20" s="7">
         <v>7</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="H20" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="D21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="7">
+        <v>5</v>
+      </c>
+      <c r="G21" s="7">
+        <v>7</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+    </row>
+    <row r="23" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="7">
+        <v>5</v>
+      </c>
+      <c r="G23" s="7">
+        <v>7</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+    </row>
+    <row r="25" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="7">
+        <v>5</v>
+      </c>
+      <c r="G25" s="7">
+        <v>7</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="7">
+        <v>5</v>
+      </c>
+      <c r="G26" s="7">
+        <v>7</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27" s="7">
+        <v>5</v>
+      </c>
+      <c r="G27" s="7">
+        <v>7</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="7">
+        <v>5</v>
+      </c>
+      <c r="G28" s="7">
+        <v>7</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="7">
+        <v>5</v>
+      </c>
+      <c r="G29" s="7">
+        <v>7</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F30" s="7">
+        <v>5</v>
+      </c>
+      <c r="G30" s="7">
+        <v>7</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="7">
+        <v>5</v>
+      </c>
+      <c r="G31" s="7">
+        <v>7</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" s="7">
+        <v>5</v>
+      </c>
+      <c r="G32" s="7">
+        <v>7</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="7">
+        <v>5</v>
+      </c>
+      <c r="G33" s="7">
+        <v>7</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+    </row>
+    <row r="35" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="7">
+        <v>5</v>
+      </c>
+      <c r="G35" s="7">
+        <v>7</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="8">
+    </row>
+    <row r="36" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F36" s="7">
         <v>5</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G36" s="7">
         <v>7</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="H36" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="8">
+      <c r="D37" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="7">
         <v>5</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G37" s="7">
         <v>7</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="H37" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="8">
+      <c r="D38" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38" s="7">
         <v>5</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G38" s="7">
         <v>7</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="H38" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+    </row>
+    <row r="40" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="8">
+      <c r="D40" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F40" s="7">
         <v>5</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G40" s="7">
         <v>7</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="H40" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="8">
+      <c r="D41" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F41" s="7">
         <v>5</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G41" s="7">
         <v>7</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="H41" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+    </row>
+    <row r="43" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="8">
+      <c r="D43" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F43" s="7">
         <v>5</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G43" s="7">
         <v>7</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="H43" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+    </row>
+    <row r="45" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="8">
+      <c r="D45" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F45" s="7">
         <v>5</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G45" s="7">
         <v>7</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="8">
-        <v>5</v>
-      </c>
-      <c r="G16" s="8">
-        <v>7</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="8">
-        <v>5</v>
-      </c>
-      <c r="G17" s="8">
-        <v>7</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-    </row>
-    <row r="19" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" s="8">
-        <v>5</v>
-      </c>
-      <c r="G19" s="8">
-        <v>7</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F20" s="8">
-        <v>5</v>
-      </c>
-      <c r="G20" s="8">
-        <v>7</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="8">
-        <v>5</v>
-      </c>
-      <c r="G21" s="8">
-        <v>7</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-    </row>
-    <row r="23" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="8">
-        <v>5</v>
-      </c>
-      <c r="G23" s="8">
-        <v>7</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-    </row>
-    <row r="25" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="F25" s="8">
-        <v>5</v>
-      </c>
-      <c r="G25" s="8">
-        <v>7</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F26" s="8">
-        <v>5</v>
-      </c>
-      <c r="G26" s="8">
-        <v>7</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27" s="8">
-        <v>5</v>
-      </c>
-      <c r="G27" s="8">
-        <v>7</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F28" s="8">
-        <v>5</v>
-      </c>
-      <c r="G28" s="8">
-        <v>7</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F29" s="8">
-        <v>5</v>
-      </c>
-      <c r="G29" s="8">
-        <v>7</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F30" s="8">
-        <v>5</v>
-      </c>
-      <c r="G30" s="8">
-        <v>7</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F31" s="8">
-        <v>5</v>
-      </c>
-      <c r="G31" s="8">
-        <v>7</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F32" s="8">
-        <v>5</v>
-      </c>
-      <c r="G32" s="8">
-        <v>7</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" s="8">
-        <v>5</v>
-      </c>
-      <c r="G33" s="8">
-        <v>7</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-    </row>
-    <row r="35" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F35" s="8">
-        <v>5</v>
-      </c>
-      <c r="G35" s="8">
-        <v>7</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F36" s="8">
-        <v>5</v>
-      </c>
-      <c r="G36" s="8">
-        <v>7</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="F37" s="8">
-        <v>5</v>
-      </c>
-      <c r="G37" s="8">
-        <v>7</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F38" s="8">
-        <v>5</v>
-      </c>
-      <c r="G38" s="8">
-        <v>7</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-    </row>
-    <row r="40" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F40" s="8">
-        <v>5</v>
-      </c>
-      <c r="G40" s="8">
-        <v>7</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F41" s="8">
-        <v>5</v>
-      </c>
-      <c r="G41" s="8">
-        <v>7</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-    </row>
-    <row r="43" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="F43" s="8">
-        <v>5</v>
-      </c>
-      <c r="G43" s="8">
-        <v>7</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-    </row>
-    <row r="45" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F45" s="8">
-        <v>5</v>
-      </c>
-      <c r="G45" s="8">
-        <v>7</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>59</v>
+      <c r="H45" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4314,1384 +4267,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D6B611-C79A-4628-842F-788DD2B12556}">
-  <dimension ref="A1:AJ38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="16">
-        <v>45979</v>
-      </c>
-      <c r="E1" s="16">
-        <v>45980</v>
-      </c>
-      <c r="F1" s="16">
-        <v>45981</v>
-      </c>
-      <c r="G1" s="16">
-        <v>45982</v>
-      </c>
-      <c r="H1" s="16">
-        <v>45983</v>
-      </c>
-      <c r="I1" s="16">
-        <v>45984</v>
-      </c>
-      <c r="J1" s="16">
-        <v>45985</v>
-      </c>
-      <c r="K1" s="16">
-        <v>45986</v>
-      </c>
-      <c r="L1" s="16">
-        <v>45987</v>
-      </c>
-      <c r="M1" s="16">
-        <v>45988</v>
-      </c>
-      <c r="N1" s="16">
-        <v>45989</v>
-      </c>
-      <c r="O1" s="16">
-        <v>45990</v>
-      </c>
-      <c r="P1" s="16">
-        <v>45991</v>
-      </c>
-      <c r="Q1" s="16">
-        <v>45992</v>
-      </c>
-      <c r="R1" s="16">
-        <v>45993</v>
-      </c>
-      <c r="S1" s="16">
-        <v>45994</v>
-      </c>
-      <c r="T1" s="16">
-        <v>45995</v>
-      </c>
-      <c r="U1" s="16">
-        <v>45996</v>
-      </c>
-      <c r="V1" s="16">
-        <v>45997</v>
-      </c>
-      <c r="W1" s="16">
-        <v>45998</v>
-      </c>
-      <c r="X1" s="16">
-        <v>45999</v>
-      </c>
-      <c r="Y1" s="16">
-        <v>46000</v>
-      </c>
-      <c r="Z1" s="16">
-        <v>46001</v>
-      </c>
-      <c r="AA1" s="16">
-        <v>46002</v>
-      </c>
-      <c r="AB1" s="16">
-        <v>46003</v>
-      </c>
-      <c r="AC1" s="16">
-        <v>46004</v>
-      </c>
-      <c r="AD1" s="16">
-        <v>46005</v>
-      </c>
-      <c r="AE1" s="16">
-        <v>46006</v>
-      </c>
-      <c r="AF1" s="16">
-        <v>46007</v>
-      </c>
-      <c r="AG1" s="16">
-        <v>46008</v>
-      </c>
-      <c r="AH1" s="16">
-        <v>46009</v>
-      </c>
-      <c r="AI1" s="16">
-        <v>46010</v>
-      </c>
-      <c r="AJ1" s="16">
-        <v>46011</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-    </row>
-    <row r="3" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="10"/>
-      <c r="AC3" s="10"/>
-      <c r="AD3" s="10"/>
-      <c r="AE3" s="10"/>
-      <c r="AF3" s="10"/>
-      <c r="AG3" s="10"/>
-    </row>
-    <row r="4" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10"/>
-      <c r="AF4" s="10"/>
-      <c r="AG4" s="10"/>
-    </row>
-    <row r="5" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
-      <c r="AE5" s="10"/>
-      <c r="AF5" s="10"/>
-      <c r="AG5" s="10"/>
-    </row>
-    <row r="6" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10"/>
-      <c r="AA6" s="10"/>
-      <c r="AB6" s="10"/>
-      <c r="AC6" s="10"/>
-      <c r="AD6" s="10"/>
-      <c r="AE6" s="10"/>
-      <c r="AF6" s="10"/>
-      <c r="AG6" s="10"/>
-    </row>
-    <row r="7" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="10"/>
-      <c r="AC7" s="10"/>
-      <c r="AD7" s="10"/>
-      <c r="AE7" s="10"/>
-      <c r="AF7" s="10"/>
-      <c r="AG7" s="10"/>
-    </row>
-    <row r="8" spans="1:36" ht="57" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="10"/>
-      <c r="AC8" s="10"/>
-      <c r="AD8" s="10"/>
-      <c r="AE8" s="10"/>
-      <c r="AF8" s="10"/>
-      <c r="AG8" s="10"/>
-    </row>
-    <row r="9" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10"/>
-      <c r="AA9" s="10"/>
-      <c r="AB9" s="10"/>
-      <c r="AC9" s="10"/>
-      <c r="AD9" s="10"/>
-      <c r="AE9" s="10"/>
-      <c r="AF9" s="10"/>
-      <c r="AG9" s="10"/>
-    </row>
-    <row r="10" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="10"/>
-      <c r="AA10" s="10"/>
-      <c r="AB10" s="10"/>
-      <c r="AC10" s="10"/>
-      <c r="AD10" s="10"/>
-      <c r="AE10" s="10"/>
-      <c r="AF10" s="10"/>
-      <c r="AG10" s="10"/>
-    </row>
-    <row r="11" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-      <c r="AA11" s="10"/>
-      <c r="AB11" s="10"/>
-      <c r="AC11" s="10"/>
-      <c r="AD11" s="10"/>
-      <c r="AE11" s="10"/>
-      <c r="AF11" s="10"/>
-      <c r="AG11" s="10"/>
-    </row>
-    <row r="12" spans="1:36" ht="57" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-      <c r="AB12" s="10"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
-      <c r="AF12" s="10"/>
-      <c r="AG12" s="10"/>
-    </row>
-    <row r="13" spans="1:36" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-      <c r="AA13" s="10"/>
-      <c r="AB13" s="10"/>
-      <c r="AC13" s="10"/>
-      <c r="AD13" s="10"/>
-      <c r="AE13" s="10"/>
-      <c r="AF13" s="10"/>
-      <c r="AG13" s="10"/>
-    </row>
-    <row r="14" spans="1:36" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="16">
-        <v>39583</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10"/>
-      <c r="AA14" s="10"/>
-      <c r="AB14" s="10"/>
-      <c r="AC14" s="10"/>
-      <c r="AD14" s="10"/>
-      <c r="AE14" s="10"/>
-      <c r="AF14" s="10"/>
-      <c r="AG14" s="10"/>
-    </row>
-    <row r="15" spans="1:36" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
-      <c r="AA15" s="10"/>
-      <c r="AB15" s="10"/>
-      <c r="AC15" s="10"/>
-      <c r="AD15" s="10"/>
-      <c r="AE15" s="10"/>
-      <c r="AF15" s="10"/>
-      <c r="AG15" s="10"/>
-    </row>
-    <row r="16" spans="1:36" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="10"/>
-      <c r="AB16" s="10"/>
-      <c r="AC16" s="10"/>
-      <c r="AD16" s="10"/>
-      <c r="AE16" s="10"/>
-      <c r="AF16" s="10"/>
-      <c r="AG16" s="10"/>
-    </row>
-    <row r="17" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10"/>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="10"/>
-      <c r="Z17" s="10"/>
-      <c r="AA17" s="10"/>
-      <c r="AB17" s="10"/>
-      <c r="AC17" s="10"/>
-      <c r="AD17" s="10"/>
-      <c r="AE17" s="10"/>
-      <c r="AF17" s="10"/>
-      <c r="AG17" s="10"/>
-    </row>
-    <row r="18" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
-      <c r="AB18" s="10"/>
-      <c r="AC18" s="10"/>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="10"/>
-      <c r="AF18" s="10"/>
-      <c r="AG18" s="10"/>
-    </row>
-    <row r="19" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10"/>
-      <c r="Y19" s="10"/>
-      <c r="Z19" s="10"/>
-      <c r="AA19" s="10"/>
-      <c r="AB19" s="10"/>
-      <c r="AC19" s="10"/>
-      <c r="AD19" s="10"/>
-      <c r="AE19" s="10"/>
-      <c r="AF19" s="10"/>
-      <c r="AG19" s="10"/>
-    </row>
-    <row r="20" spans="1:33" ht="57" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
-      <c r="W20" s="10"/>
-      <c r="X20" s="10"/>
-      <c r="Y20" s="10"/>
-      <c r="Z20" s="10"/>
-      <c r="AA20" s="10"/>
-      <c r="AB20" s="10"/>
-      <c r="AC20" s="10"/>
-      <c r="AD20" s="10"/>
-      <c r="AE20" s="10"/>
-      <c r="AF20" s="10"/>
-      <c r="AG20" s="10"/>
-    </row>
-    <row r="21" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
-      <c r="T21" s="10"/>
-      <c r="U21" s="10"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="10"/>
-      <c r="Y21" s="10"/>
-      <c r="Z21" s="10"/>
-      <c r="AA21" s="10"/>
-      <c r="AB21" s="10"/>
-      <c r="AC21" s="10"/>
-      <c r="AD21" s="10"/>
-      <c r="AE21" s="10"/>
-      <c r="AF21" s="10"/>
-      <c r="AG21" s="10"/>
-    </row>
-    <row r="22" spans="1:33" ht="57" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
-      <c r="U22" s="10"/>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="10"/>
-      <c r="Y22" s="10"/>
-      <c r="Z22" s="10"/>
-      <c r="AA22" s="10"/>
-      <c r="AB22" s="10"/>
-      <c r="AC22" s="10"/>
-      <c r="AD22" s="10"/>
-      <c r="AE22" s="10"/>
-      <c r="AF22" s="10"/>
-      <c r="AG22" s="10"/>
-    </row>
-    <row r="23" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
-      <c r="V23" s="10"/>
-      <c r="W23" s="10"/>
-      <c r="X23" s="10"/>
-      <c r="Y23" s="10"/>
-      <c r="Z23" s="10"/>
-      <c r="AA23" s="10"/>
-      <c r="AB23" s="10"/>
-      <c r="AC23" s="10"/>
-      <c r="AD23" s="10"/>
-      <c r="AE23" s="10"/>
-      <c r="AF23" s="10"/>
-      <c r="AG23" s="10"/>
-    </row>
-    <row r="24" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="10"/>
-      <c r="T24" s="10"/>
-      <c r="U24" s="10"/>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10"/>
-      <c r="X24" s="10"/>
-      <c r="Y24" s="10"/>
-      <c r="Z24" s="10"/>
-      <c r="AA24" s="10"/>
-      <c r="AB24" s="10"/>
-      <c r="AC24" s="10"/>
-      <c r="AD24" s="10"/>
-      <c r="AE24" s="10"/>
-      <c r="AF24" s="10"/>
-      <c r="AG24" s="10"/>
-    </row>
-    <row r="25" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-      <c r="X25" s="10"/>
-      <c r="Y25" s="10"/>
-      <c r="Z25" s="10"/>
-      <c r="AA25" s="10"/>
-      <c r="AB25" s="10"/>
-      <c r="AC25" s="10"/>
-      <c r="AD25" s="10"/>
-      <c r="AE25" s="10"/>
-      <c r="AF25" s="10"/>
-      <c r="AG25" s="10"/>
-    </row>
-    <row r="26" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
-      <c r="U26" s="10"/>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
-      <c r="X26" s="10"/>
-      <c r="Y26" s="10"/>
-      <c r="Z26" s="10"/>
-      <c r="AA26" s="10"/>
-      <c r="AB26" s="10"/>
-      <c r="AC26" s="10"/>
-      <c r="AD26" s="10"/>
-      <c r="AE26" s="10"/>
-      <c r="AF26" s="10"/>
-      <c r="AG26" s="10"/>
-    </row>
-    <row r="27" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
-      <c r="T27" s="10"/>
-      <c r="U27" s="10"/>
-      <c r="V27" s="10"/>
-      <c r="W27" s="10"/>
-      <c r="X27" s="10"/>
-      <c r="Y27" s="10"/>
-      <c r="Z27" s="10"/>
-      <c r="AA27" s="10"/>
-      <c r="AB27" s="10"/>
-      <c r="AC27" s="10"/>
-      <c r="AD27" s="10"/>
-      <c r="AE27" s="10"/>
-      <c r="AF27" s="10"/>
-      <c r="AG27" s="10"/>
-    </row>
-    <row r="28" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
-      <c r="S28" s="10"/>
-      <c r="T28" s="10"/>
-      <c r="U28" s="10"/>
-      <c r="V28" s="10"/>
-      <c r="W28" s="10"/>
-      <c r="X28" s="10"/>
-      <c r="Y28" s="10"/>
-      <c r="Z28" s="10"/>
-      <c r="AA28" s="10"/>
-      <c r="AB28" s="10"/>
-      <c r="AC28" s="10"/>
-      <c r="AD28" s="10"/>
-      <c r="AE28" s="10"/>
-      <c r="AF28" s="10"/>
-      <c r="AG28" s="10"/>
-    </row>
-    <row r="29" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10"/>
-      <c r="T29" s="10"/>
-      <c r="U29" s="10"/>
-      <c r="V29" s="10"/>
-      <c r="W29" s="10"/>
-      <c r="X29" s="10"/>
-      <c r="Y29" s="10"/>
-      <c r="Z29" s="10"/>
-      <c r="AA29" s="10"/>
-      <c r="AB29" s="10"/>
-      <c r="AC29" s="10"/>
-      <c r="AD29" s="10"/>
-      <c r="AE29" s="10"/>
-      <c r="AF29" s="10"/>
-      <c r="AG29" s="10"/>
-    </row>
-    <row r="30" spans="1:33" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10"/>
-      <c r="U30" s="10"/>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="10"/>
-      <c r="Y30" s="10"/>
-      <c r="Z30" s="10"/>
-      <c r="AA30" s="10"/>
-      <c r="AB30" s="10"/>
-      <c r="AC30" s="10"/>
-      <c r="AD30" s="10"/>
-      <c r="AE30" s="10"/>
-      <c r="AF30" s="10"/>
-      <c r="AG30" s="10"/>
-    </row>
-    <row r="31" spans="1:33" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
-      <c r="U31" s="10"/>
-      <c r="V31" s="10"/>
-      <c r="W31" s="10"/>
-      <c r="X31" s="10"/>
-      <c r="Y31" s="10"/>
-      <c r="Z31" s="10"/>
-      <c r="AA31" s="10"/>
-      <c r="AB31" s="10"/>
-      <c r="AC31" s="10"/>
-      <c r="AD31" s="10"/>
-      <c r="AE31" s="10"/>
-      <c r="AF31" s="10"/>
-      <c r="AG31" s="10"/>
-    </row>
-    <row r="32" spans="1:33" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="10"/>
-      <c r="S32" s="10"/>
-      <c r="T32" s="10"/>
-      <c r="U32" s="10"/>
-      <c r="V32" s="10"/>
-      <c r="W32" s="10"/>
-      <c r="X32" s="10"/>
-      <c r="Y32" s="10"/>
-      <c r="Z32" s="10"/>
-      <c r="AA32" s="10"/>
-      <c r="AB32" s="10"/>
-      <c r="AC32" s="10"/>
-      <c r="AD32" s="10"/>
-      <c r="AE32" s="10"/>
-      <c r="AF32" s="10"/>
-      <c r="AG32" s="10"/>
-    </row>
-    <row r="33" spans="1:33" ht="57" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
-      <c r="U33" s="10"/>
-      <c r="V33" s="10"/>
-      <c r="W33" s="10"/>
-      <c r="X33" s="10"/>
-      <c r="Y33" s="10"/>
-      <c r="Z33" s="10"/>
-      <c r="AA33" s="10"/>
-      <c r="AB33" s="10"/>
-      <c r="AC33" s="10"/>
-      <c r="AD33" s="10"/>
-      <c r="AE33" s="10"/>
-      <c r="AF33" s="10"/>
-      <c r="AG33" s="10"/>
-    </row>
-    <row r="34" spans="1:33" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10"/>
-      <c r="U34" s="10"/>
-      <c r="V34" s="10"/>
-      <c r="W34" s="10"/>
-      <c r="X34" s="10"/>
-      <c r="Y34" s="10"/>
-      <c r="Z34" s="10"/>
-      <c r="AA34" s="10"/>
-      <c r="AB34" s="10"/>
-      <c r="AC34" s="10"/>
-      <c r="AD34" s="10"/>
-      <c r="AE34" s="10"/>
-      <c r="AF34" s="10"/>
-      <c r="AG34" s="10"/>
-    </row>
-    <row r="36" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="E36" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="E37" s="10"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="13"/>
-    </row>
-    <row r="38" spans="1:33" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="B38" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5727,36 +4302,36 @@
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="31"/>
+      <c r="B4" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="5" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="B5" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5823,13 +4398,13 @@
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="28"/>
+      <c r="B16" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
@@ -5881,69 +4456,69 @@
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="31"/>
+      <c r="B24" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="22"/>
     </row>
     <row r="25" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="F26" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>168</v>
+      <c r="B27" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
+      <c r="B28" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="25"/>
     </row>
     <row r="29" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="2"/>
@@ -6023,13 +4598,13 @@
       <c r="F39" s="2"/>
     </row>
     <row r="40" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="28"/>
+      <c r="B40" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="19"/>
     </row>
     <row r="41" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="2"/>
@@ -6123,13 +4698,13 @@
       <c r="F53" s="2"/>
     </row>
     <row r="54" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="28"/>
+      <c r="B54" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="19"/>
     </row>
     <row r="55" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="2"/>
@@ -6230,13 +4805,13 @@
       <c r="F68" s="2"/>
     </row>
     <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C69" s="27"/>
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="28"/>
+      <c r="B69" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="19"/>
     </row>
     <row r="70" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="2"/>
@@ -6323,13 +4898,13 @@
       <c r="F81" s="2"/>
     </row>
     <row r="82" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="C82" s="27"/>
-      <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
-      <c r="F82" s="28"/>
+      <c r="B82" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="19"/>
     </row>
     <row r="83" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="2"/>
@@ -6402,13 +4977,13 @@
       <c r="F92" s="2"/>
     </row>
     <row r="93" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B93" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C93" s="27"/>
-      <c r="D93" s="27"/>
-      <c r="E93" s="27"/>
-      <c r="F93" s="28"/>
+      <c r="B93" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="19"/>
     </row>
     <row r="94" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="2"/>
@@ -7365,308 +5940,1210 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E79EAF51-6346-4E0C-850A-7884848EE0FC}">
-  <dimension ref="C4:E17"/>
+  <dimension ref="B1:T16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="3.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="30.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" customWidth="1"/>
+    <col min="15" max="15" width="30.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" customWidth="1"/>
+    <col min="19" max="19" width="30.7109375" customWidth="1"/>
+    <col min="20" max="20" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C4" s="20" t="s">
+    <row r="1" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="F3" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="J3" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="N3" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="12"/>
+      <c r="R3" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="12"/>
+    </row>
+    <row r="4" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="F4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="J4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="N4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="R4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+    </row>
+    <row r="5" spans="2:20" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="F5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="J5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="N5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="R5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+    </row>
+    <row r="6" spans="2:20" ht="30" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="F6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B7" s="13">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13">
+        <v>8</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="F7" s="13">
+        <v>5</v>
+      </c>
+      <c r="G7" s="13">
+        <v>8</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="J7" s="13">
+        <v>5</v>
+      </c>
+      <c r="K7" s="13">
+        <v>8</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="N7" s="13">
+        <v>5</v>
+      </c>
+      <c r="O7" s="13">
+        <v>8</v>
+      </c>
+      <c r="P7" s="12"/>
+      <c r="R7" s="13">
+        <v>5</v>
+      </c>
+      <c r="S7" s="13">
+        <v>8</v>
+      </c>
+      <c r="T7" s="12"/>
+    </row>
+    <row r="8" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="F8" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="J8" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="N8" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="R8" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C5" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="21"/>
-    </row>
-    <row r="6" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C6" s="35" t="s">
+      <c r="F9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-    </row>
-    <row r="7" spans="3:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-    </row>
-    <row r="8" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C8" s="20" t="s">
+      <c r="H9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="R10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="S10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="T10" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="B11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="R11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="S11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="T11" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="R12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="S12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="T12" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="T13" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" ht="30" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="C14" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="3:5" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C9" s="22">
-        <v>5</v>
-      </c>
-      <c r="D9" s="22">
-        <v>8</v>
-      </c>
-      <c r="E9" s="21"/>
-    </row>
-    <row r="10" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C10" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C11" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="C12" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C13" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="C14" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C15" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C16" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="D14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="R14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C10:E10"/>
+  <mergeCells count="15">
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="R5:T5"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F8:H8"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E03081-6D4B-48F0-9762-CB959C944999}">
-  <dimension ref="C4:E17"/>
+  <dimension ref="B2:T15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="3.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="10" max="11" width="30.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" customWidth="1"/>
+    <col min="15" max="15" width="30.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" customWidth="1"/>
+    <col min="19" max="19" width="30.7109375" customWidth="1"/>
+    <col min="20" max="20" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C4" s="20" t="s">
+    <row r="2" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="F3" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="J3" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="N3" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" s="12"/>
+      <c r="R3" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="T3" s="12"/>
+    </row>
+    <row r="4" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="F4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="J4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="N4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="R4" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+    </row>
+    <row r="5" spans="2:20" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="F5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="J5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="N5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="R5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+    </row>
+    <row r="6" spans="2:20" ht="30" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="F6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B7" s="13">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13">
+        <v>8</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="F7" s="13">
+        <v>5</v>
+      </c>
+      <c r="G7" s="13">
+        <v>8</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="J7" s="13">
+        <v>5</v>
+      </c>
+      <c r="K7" s="13">
+        <v>8</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="N7" s="13">
+        <v>5</v>
+      </c>
+      <c r="O7" s="13">
+        <v>8</v>
+      </c>
+      <c r="P7" s="12"/>
+      <c r="R7" s="13">
+        <v>5</v>
+      </c>
+      <c r="S7" s="13">
+        <v>8</v>
+      </c>
+      <c r="T7" s="12"/>
+    </row>
+    <row r="8" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="F8" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="J8" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="N8" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="R8" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C5" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="21"/>
-    </row>
-    <row r="6" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C6" s="35" t="s">
+      <c r="F9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-    </row>
-    <row r="7" spans="3:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-    </row>
-    <row r="8" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C8" s="20" t="s">
+      <c r="H9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="R10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="S10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="T10" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="B11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="R11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="S11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="T11" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="R12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="S12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="T12" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="T13" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" ht="30" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="C14" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="3:5" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C9" s="22">
-        <v>5</v>
-      </c>
-      <c r="D9" s="22">
-        <v>8</v>
-      </c>
-      <c r="E9" s="21"/>
-    </row>
-    <row r="10" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C10" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C11" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="C12" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C13" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="C14" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-    </row>
-    <row r="16" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C16" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="D14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="R14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C10:E10"/>
+  <mergeCells count="15">
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:T5"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D2BA1A-E3EC-4B05-B9AB-FCC72E25559E}">
   <dimension ref="C4:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -7678,136 +7155,136 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C5" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="12"/>
+    </row>
+    <row r="6" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+    </row>
+    <row r="7" spans="3:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+    </row>
+    <row r="8" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C8" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="20" t="s">
+    </row>
+    <row r="9" spans="3:5" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C9" s="13">
+        <v>5</v>
+      </c>
+      <c r="D9" s="13">
+        <v>8</v>
+      </c>
+      <c r="E9" s="12"/>
+    </row>
+    <row r="10" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C10" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C5" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="21"/>
-    </row>
-    <row r="6" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C6" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-    </row>
-    <row r="7" spans="3:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-    </row>
-    <row r="8" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C8" s="20" t="s">
+    <row r="12" spans="3:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C12" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C13" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="C14" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C15" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="C16" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D16" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="3:5" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C9" s="22">
-        <v>5</v>
-      </c>
-      <c r="D9" s="22">
-        <v>8</v>
-      </c>
-      <c r="E9" s="21"/>
-    </row>
-    <row r="10" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C10" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C11" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="C12" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C13" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="C14" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C15" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C16" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>156</v>
+      <c r="E16" s="11" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/01_proyecto/trim1/01_contextualizacion_proyecto/PL01 - Plantilla de Definición.xlsx
+++ b/01_proyecto/trim1/01_contextualizacion_proyecto/PL01 - Plantilla de Definición.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZUS\Desktop\Innovation_Fusion\01_proyecto\trim1\01_contextualizacion_proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350B04CA-0AD3-43B7-BCBA-29F0D2C06655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F829CC4C-4ECF-4E91-A7C0-9966A45CE2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipo" sheetId="1" r:id="rId1"/>
@@ -18,19 +18,24 @@
     <sheet name="Historia de Usuario" sheetId="3" r:id="rId3"/>
     <sheet name="Gestión de Usuarios y Autentica" sheetId="6" r:id="rId4"/>
     <sheet name="Catálogo y Experiencia de Naveg" sheetId="7" r:id="rId5"/>
-    <sheet name="Gestión de Productos e Inventar" sheetId="5" r:id="rId6"/>
+    <sheet name="Gestión de Productos e Inventar" sheetId="8" r:id="rId6"/>
+    <sheet name="Gestión de Promociones" sheetId="9" r:id="rId7"/>
+    <sheet name="Carrito y Checkout" sheetId="10" r:id="rId8"/>
+    <sheet name="Gestión de Devoluciones" sheetId="11" r:id="rId9"/>
+    <sheet name="Atención y Soporte al Cliente" sheetId="12" r:id="rId10"/>
+    <sheet name="Reportes y Administración Avanz" sheetId="13" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="+CJhT1B5jpkQwxSTxyNLk1YCzpn9UEauZYMdiwIpMNk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId12" roundtripDataChecksum="+CJhT1B5jpkQwxSTxyNLk1YCzpn9UEauZYMdiwIpMNk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="187">
   <si>
     <t>#</t>
   </si>
@@ -589,6 +594,12 @@
   </si>
   <si>
     <t>HU_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurar precios y descuentos de los productos </t>
+  </si>
+  <si>
+    <t>Atención y Soporte al Cliente</t>
   </si>
 </sst>
 </file>
@@ -925,6 +936,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -959,9 +973,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2388,6 +2399,322 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F8147E-37D2-41AD-9965-F04F594ADC86}">
+  <dimension ref="B1:D16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D3" s="12"/>
+    </row>
+    <row r="4" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+    </row>
+    <row r="5" spans="2:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+    </row>
+    <row r="6" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B7" s="13">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13">
+        <v>8</v>
+      </c>
+      <c r="D7" s="12"/>
+    </row>
+    <row r="8" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B8:D8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{218130F5-64A5-4982-AF5F-1C1575E940E3}">
+  <dimension ref="B1:D16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="12"/>
+    </row>
+    <row r="4" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+    </row>
+    <row r="5" spans="2:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+    </row>
+    <row r="6" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B7" s="13">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13">
+        <v>8</v>
+      </c>
+      <c r="D7" s="12"/>
+    </row>
+    <row r="8" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B8:D8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
@@ -2430,15 +2757,15 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
     </row>
     <row r="5" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="6" t="s">
@@ -2556,15 +2883,15 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="6" t="s">
@@ -2728,15 +3055,15 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -2808,15 +3135,15 @@
       </c>
     </row>
     <row r="22" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="7" t="s">
@@ -2842,15 +3169,15 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
@@ -3060,15 +3387,15 @@
       </c>
     </row>
     <row r="34" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
@@ -3163,15 +3490,15 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
     </row>
     <row r="40" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="7" t="s">
@@ -3220,15 +3547,15 @@
       </c>
     </row>
     <row r="42" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
     </row>
     <row r="43" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="7" t="s">
@@ -3254,15 +3581,15 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
     </row>
     <row r="45" spans="2:8" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="7" t="s">
@@ -4302,13 +4629,13 @@
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
     </row>
     <row r="5" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="9" t="s">
@@ -4398,13 +4725,13 @@
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="20"/>
     </row>
     <row r="17" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
@@ -4456,13 +4783,13 @@
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="23"/>
     </row>
     <row r="25" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
@@ -4512,13 +4839,13 @@
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="26"/>
     </row>
     <row r="29" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="2"/>
@@ -4598,13 +4925,13 @@
       <c r="F39" s="2"/>
     </row>
     <row r="40" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="20"/>
     </row>
     <row r="41" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="2"/>
@@ -4698,13 +5025,13 @@
       <c r="F53" s="2"/>
     </row>
     <row r="54" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="20"/>
     </row>
     <row r="55" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="2"/>
@@ -4805,13 +5132,13 @@
       <c r="F68" s="2"/>
     </row>
     <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="20"/>
     </row>
     <row r="70" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="2"/>
@@ -4898,13 +5225,13 @@
       <c r="F81" s="2"/>
     </row>
     <row r="82" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="17" t="s">
+      <c r="B82" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C82" s="18"/>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18"/>
-      <c r="F82" s="19"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="19"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="20"/>
     </row>
     <row r="83" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="2"/>
@@ -4977,13 +5304,13 @@
       <c r="F92" s="2"/>
     </row>
     <row r="93" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B93" s="17" t="s">
+      <c r="B93" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18"/>
-      <c r="E93" s="18"/>
-      <c r="F93" s="19"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="19"/>
+      <c r="E93" s="19"/>
+      <c r="F93" s="20"/>
     </row>
     <row r="94" spans="2:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="2"/>
@@ -6048,60 +6375,60 @@
       <c r="T3" s="12"/>
     </row>
     <row r="4" spans="2:20" ht="15" x14ac:dyDescent="0.2">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="F4" s="26" t="s">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="F4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="J4" s="26" t="s">
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="J4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="N4" s="26" t="s">
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="N4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="R4" s="26" t="s">
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="R4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
     </row>
     <row r="5" spans="2:20" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="F5" s="27" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="F5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="J5" s="27" t="s">
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="J5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="N5" s="27" t="s">
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="N5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="R5" s="27" t="s">
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="R5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-    </row>
-    <row r="6" spans="2:20" ht="30" x14ac:dyDescent="0.2">
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+    </row>
+    <row r="6" spans="2:20" ht="15" x14ac:dyDescent="0.2">
       <c r="B6" s="11" t="s">
         <v>152</v>
       </c>
@@ -6186,31 +6513,31 @@
       <c r="T7" s="12"/>
     </row>
     <row r="8" spans="2:20" ht="15" x14ac:dyDescent="0.2">
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="F8" s="26" t="s">
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="F8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="J8" s="26" t="s">
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="J8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="N8" s="26" t="s">
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="N8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="R8" s="26" t="s">
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="R8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B9" s="14" t="s">
@@ -6259,7 +6586,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="10" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:20" ht="51" x14ac:dyDescent="0.2">
       <c r="B10" s="12" t="s">
         <v>169</v>
       </c>
@@ -6306,7 +6633,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="2:20" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:20" ht="63.75" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>172</v>
       </c>
@@ -6353,7 +6680,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="2:20" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
         <v>173</v>
       </c>
@@ -6400,7 +6727,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B13" s="12" t="s">
         <v>179</v>
       </c>
@@ -6447,7 +6774,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="2:20" ht="30" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:20" ht="15" x14ac:dyDescent="0.2">
       <c r="B14" s="11" t="s">
         <v>157</v>
       </c>
@@ -6512,24 +6839,30 @@
       <c r="T15" s="12"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F8:H8"/>
     <mergeCell ref="R4:T4"/>
     <mergeCell ref="R5:T5"/>
     <mergeCell ref="R8:T8"/>
@@ -6539,12 +6872,6 @@
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="N5:P5"/>
     <mergeCell ref="N8:P8"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F8:H8"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6553,7 +6880,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E03081-6D4B-48F0-9762-CB959C944999}">
-  <dimension ref="B2:T15"/>
+  <dimension ref="B2:T30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -6620,7 +6947,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="2:20" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B3" s="12" t="s">
         <v>183</v>
       </c>
@@ -6658,60 +6985,60 @@
       <c r="T3" s="12"/>
     </row>
     <row r="4" spans="2:20" ht="15" x14ac:dyDescent="0.2">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="F4" s="26" t="s">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="F4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="J4" s="26" t="s">
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="J4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="N4" s="26" t="s">
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="N4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="R4" s="26" t="s">
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="R4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
     </row>
     <row r="5" spans="2:20" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="F5" s="27" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="F5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="J5" s="27" t="s">
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="J5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="N5" s="27" t="s">
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="N5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="R5" s="27" t="s">
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="R5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-    </row>
-    <row r="6" spans="2:20" ht="30" x14ac:dyDescent="0.2">
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+    </row>
+    <row r="6" spans="2:20" ht="15" x14ac:dyDescent="0.2">
       <c r="B6" s="11" t="s">
         <v>152</v>
       </c>
@@ -6796,31 +7123,31 @@
       <c r="T7" s="12"/>
     </row>
     <row r="8" spans="2:20" ht="15" x14ac:dyDescent="0.2">
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="F8" s="26" t="s">
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="F8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="J8" s="26" t="s">
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="J8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="N8" s="26" t="s">
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="N8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="R8" s="26" t="s">
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="R8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B9" s="14" t="s">
@@ -6869,7 +7196,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="10" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:20" ht="51" x14ac:dyDescent="0.2">
       <c r="B10" s="12" t="s">
         <v>169</v>
       </c>
@@ -6916,7 +7243,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="2:20" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:20" ht="63.75" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>172</v>
       </c>
@@ -6963,7 +7290,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="2:20" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
         <v>173</v>
       </c>
@@ -7010,7 +7337,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B13" s="12" t="s">
         <v>179</v>
       </c>
@@ -7057,7 +7384,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="2:20" ht="30" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:20" ht="15" x14ac:dyDescent="0.2">
       <c r="B14" s="11" t="s">
         <v>157</v>
       </c>
@@ -7121,178 +7448,2127 @@
       <c r="S15" s="12"/>
       <c r="T15" s="12"/>
     </row>
+    <row r="17" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B18" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="F18" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="F19" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="F20" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+    </row>
+    <row r="21" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B22" s="13">
+        <v>5</v>
+      </c>
+      <c r="C22" s="13">
+        <v>8</v>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="F22" s="13">
+        <v>5</v>
+      </c>
+      <c r="G22" s="13">
+        <v>8</v>
+      </c>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="F23" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="B25" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="B26" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B27" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B28" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B29" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="21">
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:T5"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="R4:T4"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="R5:T5"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D2BA1A-E3EC-4B05-B9AB-FCC72E25559E}">
-  <dimension ref="C4:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489E27E4-4C61-4BC4-AE36-B09E77141EC6}">
+  <dimension ref="B1:L16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="3.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="30.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C4" s="11" t="s">
+    <row r="1" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="B2" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="C2" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C5" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="D5" s="15" t="s">
+      <c r="F2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="12"/>
-    </row>
-    <row r="6" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C6" s="26" t="s">
+      <c r="D3" s="12"/>
+      <c r="F3" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="J3" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L3" s="12"/>
+    </row>
+    <row r="4" spans="2:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="B4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-    </row>
-    <row r="7" spans="3:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="27" t="s">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="F4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="J4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+    </row>
+    <row r="5" spans="2:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-    </row>
-    <row r="8" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C8" s="11" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="F5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="J5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+    </row>
+    <row r="6" spans="2:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="C6" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="9" spans="3:5" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C9" s="13">
+      <c r="F6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B7" s="13">
         <v>5</v>
       </c>
-      <c r="D9" s="13">
+      <c r="C7" s="13">
         <v>8</v>
       </c>
-      <c r="E9" s="12"/>
-    </row>
-    <row r="10" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C10" s="26" t="s">
+      <c r="D7" s="12"/>
+      <c r="F7" s="13">
+        <v>5</v>
+      </c>
+      <c r="G7" s="13">
+        <v>8</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="J7" s="13">
+        <v>5</v>
+      </c>
+      <c r="K7" s="13">
+        <v>8</v>
+      </c>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" spans="2:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C11" s="14" t="s">
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="F8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="J8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="C9" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="D9" s="14" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="12" spans="3:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="F9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="B11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="C12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="J5:L5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C3122D9-6023-4932-A010-29D00F97AB8B}">
+  <dimension ref="B1:D16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" s="12"/>
+    </row>
+    <row r="4" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+    </row>
+    <row r="5" spans="2:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+    </row>
+    <row r="6" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B7" s="13">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13">
+        <v>8</v>
+      </c>
+      <c r="D7" s="12"/>
+    </row>
+    <row r="8" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
         <v>169</v>
       </c>
+      <c r="C10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="B11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>171</v>
+      </c>
       <c r="D12" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
+        <v>179</v>
+      </c>
       <c r="C13" s="12" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="C14" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C15" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="E15" s="12" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="3:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C16" s="11" t="s">
+    <row r="14" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="C14" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="D14" s="11" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30FD71FA-6566-4507-8277-A0D58B677FEC}">
+  <dimension ref="B2:T30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="10" max="11" width="30.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" customWidth="1"/>
+    <col min="15" max="15" width="30.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" customWidth="1"/>
+    <col min="19" max="19" width="30.7109375" customWidth="1"/>
+    <col min="20" max="20" width="17.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="F3" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="J3" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="N3" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="P3" s="12"/>
+      <c r="R3" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="T3" s="12"/>
+    </row>
+    <row r="4" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="F4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="J4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="N4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="R4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+    </row>
+    <row r="5" spans="2:20" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="F5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="J5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="N5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="R5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+    </row>
+    <row r="6" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B7" s="13">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13">
+        <v>8</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="F7" s="13">
+        <v>5</v>
+      </c>
+      <c r="G7" s="13">
+        <v>8</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="J7" s="13">
+        <v>5</v>
+      </c>
+      <c r="K7" s="13">
+        <v>8</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="N7" s="13">
+        <v>5</v>
+      </c>
+      <c r="O7" s="13">
+        <v>8</v>
+      </c>
+      <c r="P7" s="12"/>
+      <c r="R7" s="13">
+        <v>5</v>
+      </c>
+      <c r="S7" s="13">
+        <v>8</v>
+      </c>
+      <c r="T7" s="12"/>
+    </row>
+    <row r="8" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="F8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="J8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="N8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="R8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" ht="51" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="R10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="S10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="T10" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="R11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="S11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="T11" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="R12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="S12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="T12" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="T13" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="R14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+    </row>
+    <row r="17" spans="2:16" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B18" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="F18" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="12"/>
+      <c r="J18" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="L18" s="12"/>
+      <c r="N18" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="O18" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="P18" s="12"/>
+    </row>
+    <row r="19" spans="2:16" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="F19" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="J19" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="N19" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B20" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="F20" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="J20" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="N20" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+    </row>
+    <row r="21" spans="2:16" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B22" s="13">
+        <v>5</v>
+      </c>
+      <c r="C22" s="13">
+        <v>8</v>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="F22" s="13">
+        <v>5</v>
+      </c>
+      <c r="G22" s="13">
+        <v>8</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="J22" s="13">
+        <v>5</v>
+      </c>
+      <c r="K22" s="13">
+        <v>8</v>
+      </c>
+      <c r="L22" s="12"/>
+      <c r="N22" s="13">
+        <v>5</v>
+      </c>
+      <c r="O22" s="13">
+        <v>8</v>
+      </c>
+      <c r="P22" s="12"/>
+    </row>
+    <row r="23" spans="2:16" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="F23" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="J23" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="N23" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="N24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="B25" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="O25" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="P25" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="B26" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B27" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B28" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="P28" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" ht="15" x14ac:dyDescent="0.2">
+      <c r="B29" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:T5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E290632-FEC5-4D17-94B6-28724497CC62}">
+  <dimension ref="B1:H16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="F3" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="F4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+    </row>
+    <row r="5" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="F5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+    </row>
+    <row r="6" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B7" s="13">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13">
+        <v>8</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="F7" s="13">
+        <v>5</v>
+      </c>
+      <c r="G7" s="13">
+        <v>8</v>
+      </c>
+      <c r="H7" s="12"/>
+    </row>
+    <row r="8" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="F8" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:H5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>